--- a/01_Input/00_CO Validation/Viet Nam - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Viet Nam - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="567" documentId="11_D8F61223F3A0F98994E878555E7F6C80D2E00C80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA6D38D2-3A09-45CF-849A-0316FB910986}"/>
+  <xr:revisionPtr revIDLastSave="578" documentId="11_D8F61223F3A0F98994E878555E7F6C80D2E00C80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10A67478-D793-4CF5-8345-059C659C4DD7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -236,7 +239,7 @@
     <t>N/A yet</t>
   </si>
   <si>
-    <t>Entrepreneurship Training</t>
+    <t>Medium Enterprises</t>
   </si>
   <si>
     <t>Number of enterprises reached by SHIFT's information, dissemination, capacity building and/or technical support confirm they plan to invest in renewable energy, energy efficiency or other energy transition technologies</t>
@@ -308,9 +311,6 @@
     <t>Decarbonization</t>
   </si>
   <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
     <t>Number of enterprises supported by SHIFT that have implemented technically and financially feasible pilot projects in RE, EE or other energy transition technologies</t>
   </si>
   <si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>Policy and Regulatory Frameworks</t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
   </si>
   <si>
     <t>50 kW</t>
@@ -1061,53 +1064,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1869,7 +1872,7 @@
       <c r="D11" s="51">
         <v>3000000</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="27" t="s">
         <v>55</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -1908,11 +1911,11 @@
       <c r="B12" s="67"/>
       <c r="C12" s="62"/>
       <c r="D12" s="61"/>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>60</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="9">
         <v>0</v>
@@ -1945,10 +1948,10 @@
         <v>117633</v>
       </c>
       <c r="B13" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="69" t="s">
         <v>62</v>
-      </c>
-      <c r="C13" s="69" t="s">
-        <v>63</v>
       </c>
       <c r="D13" s="51">
         <v>2201100</v>
@@ -1966,7 +1969,7 @@
         <v>0.05</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
@@ -1974,7 +1977,7 @@
         <v>26</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="7" t="s">
@@ -1993,10 +1996,10 @@
       <c r="C14" s="70"/>
       <c r="D14" s="56"/>
       <c r="E14" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" s="9">
         <v>0</v>
@@ -2005,7 +2008,7 @@
         <v>1300</v>
       </c>
       <c r="I14" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -2013,7 +2016,7 @@
         <v>26</v>
       </c>
       <c r="M14" s="41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="7" t="s">
@@ -2032,10 +2035,10 @@
       <c r="C15" s="70"/>
       <c r="D15" s="56"/>
       <c r="E15" s="27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="9">
         <v>0</v>
@@ -2044,7 +2047,7 @@
         <v>3</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
@@ -2081,7 +2084,7 @@
         <v>1600</v>
       </c>
       <c r="I16" s="47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -2106,10 +2109,10 @@
       <c r="C17" s="70"/>
       <c r="D17" s="56"/>
       <c r="E17" s="27" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17" s="9">
         <v>0</v>
@@ -2118,7 +2121,7 @@
         <v>46</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
@@ -2155,7 +2158,7 @@
         <v>6</v>
       </c>
       <c r="I18" s="47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J18" s="7"/>
       <c r="K18" s="74"/>
@@ -2172,7 +2175,7 @@
       </c>
       <c r="Q18" s="7"/>
       <c r="R18" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S18" s="7" t="s">
         <v>59</v>
@@ -2284,20 +2287,20 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="45.75">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="79">
+      <c r="D2" s="83">
         <v>896583</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>23</v>
@@ -2311,11 +2314,11 @@
       <c r="I2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="81" t="s">
+      <c r="J2" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81" t="s">
+      <c r="K2" s="76"/>
+      <c r="L2" s="76" t="s">
         <v>26</v>
       </c>
       <c r="M2" s="21"/>
@@ -2327,10 +2330,10 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="121.5">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="79"/>
+      <c r="A3" s="84"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="83"/>
       <c r="E3" s="7" t="s">
         <v>30</v>
       </c>
@@ -2346,18 +2349,18 @@
       <c r="I3" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
       <c r="M3" s="21"/>
     </row>
     <row r="4" spans="1:19" ht="259.5">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="79"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="83"/>
       <c r="E4" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>34</v>
@@ -2371,9 +2374,9 @@
       <c r="I4" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
       <c r="M4" s="40" t="s">
         <v>36</v>
       </c>
@@ -2391,18 +2394,18 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="45.75" customHeight="1">
-      <c r="A5" s="78">
+      <c r="A5" s="80">
         <v>1061012</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="91">
+      <c r="C5" s="87"/>
+      <c r="D5" s="88">
         <v>1128978</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>40</v>
@@ -2428,10 +2431,10 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="70.5" customHeight="1">
-      <c r="A6" s="78"/>
-      <c r="B6" s="88"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="91"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="85"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="88"/>
       <c r="E6" s="27" t="s">
         <v>42</v>
       </c>
@@ -2459,10 +2462,10 @@
       </c>
     </row>
     <row r="7" spans="1:19" ht="45.75">
-      <c r="A7" s="78"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="91"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="88"/>
       <c r="E7" s="27" t="s">
         <v>46</v>
       </c>
@@ -2490,10 +2493,10 @@
       </c>
     </row>
     <row r="8" spans="1:19" ht="30.75">
-      <c r="A8" s="78"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="91"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="27" t="s">
         <v>49</v>
       </c>
@@ -2515,10 +2518,10 @@
       <c r="M8" s="21"/>
     </row>
     <row r="9" spans="1:19" ht="50.25">
-      <c r="A9" s="78"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="91"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="88"/>
       <c r="E9" s="7" t="s">
         <v>30</v>
       </c>
@@ -2540,10 +2543,10 @@
       <c r="M9" s="21"/>
     </row>
     <row r="10" spans="1:19" ht="37.5">
-      <c r="A10" s="78"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="91"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="88"/>
       <c r="E10" s="27" t="str">
         <f>'Beneficiary Categories'!B15</f>
         <v>Policy or Regulatory Framework</v>
@@ -2578,20 +2581,20 @@
       </c>
     </row>
     <row r="11" spans="1:19" s="5" customFormat="1" ht="161.25" customHeight="1">
-      <c r="A11" s="76">
+      <c r="A11" s="89">
         <v>134019</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="79">
+      <c r="D11" s="83">
         <v>3000000</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>56</v>
@@ -2602,7 +2605,7 @@
       <c r="H11" s="8">
         <v>70</v>
       </c>
-      <c r="I11" s="80" t="s">
+      <c r="I11" s="91" t="s">
         <v>57</v>
       </c>
       <c r="J11" s="11"/>
@@ -2624,15 +2627,15 @@
       </c>
     </row>
     <row r="12" spans="1:19" s="6" customFormat="1" ht="91.5">
-      <c r="A12" s="76"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="79"/>
+      <c r="A12" s="89"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="83"/>
       <c r="E12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="19" t="s">
         <v>60</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="20">
         <v>0</v>
@@ -2640,7 +2643,7 @@
       <c r="H12" s="20">
         <v>20</v>
       </c>
-      <c r="I12" s="80"/>
+      <c r="I12" s="91"/>
       <c r="J12" s="34"/>
       <c r="K12" s="34"/>
       <c r="L12" s="34"/>
@@ -2660,16 +2663,16 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="183" customHeight="1">
-      <c r="A13" s="84">
+      <c r="A13" s="79">
         <v>117633</v>
       </c>
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="86" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="79">
+      <c r="D13" s="83">
         <v>2201100</v>
       </c>
       <c r="E13" s="21" t="s">
@@ -2685,15 +2688,15 @@
         <v>78</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
-      <c r="L13" s="81" t="s">
+      <c r="L13" s="76" t="s">
         <v>26</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O13" t="s">
         <v>58</v>
@@ -2703,15 +2706,15 @@
       </c>
     </row>
     <row r="14" spans="1:19" ht="168" customHeight="1">
-      <c r="A14" s="78"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="79"/>
+      <c r="A14" s="80"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="83"/>
       <c r="E14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" s="13">
         <v>0</v>
@@ -2720,13 +2723,13 @@
         <v>1300</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21"/>
-      <c r="L14" s="82"/>
+      <c r="L14" s="77"/>
       <c r="M14" s="41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O14" t="s">
         <v>58</v>
@@ -2736,15 +2739,15 @@
       </c>
     </row>
     <row r="15" spans="1:19" ht="30.75">
-      <c r="A15" s="78"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="79"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="83"/>
       <c r="E15" s="35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
@@ -2753,11 +2756,11 @@
         <v>3</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
-      <c r="L15" s="82"/>
+      <c r="L15" s="77"/>
       <c r="M15" s="21"/>
       <c r="O15" t="s">
         <v>58</v>
@@ -2767,10 +2770,10 @@
       </c>
     </row>
     <row r="16" spans="1:19" ht="76.5">
-      <c r="A16" s="78"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="79"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="83"/>
       <c r="E16" s="21" t="s">
         <v>79</v>
       </c>
@@ -2784,11 +2787,11 @@
         <v>1600</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21"/>
-      <c r="L16" s="82"/>
+      <c r="L16" s="77"/>
       <c r="M16" s="21"/>
       <c r="O16" t="s">
         <v>58</v>
@@ -2798,15 +2801,15 @@
       </c>
     </row>
     <row r="17" spans="1:19" ht="76.5">
-      <c r="A17" s="78"/>
-      <c r="B17" s="85"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="79"/>
+      <c r="A17" s="80"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="83"/>
       <c r="E17" s="35" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
@@ -2815,11 +2818,11 @@
         <v>46</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
-      <c r="L17" s="82"/>
+      <c r="L17" s="77"/>
       <c r="M17" s="21"/>
       <c r="O17" t="s">
         <v>58</v>
@@ -2829,10 +2832,10 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="121.5">
-      <c r="A18" s="78"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="79"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="83"/>
       <c r="E18" s="21" t="s">
         <v>80</v>
       </c>
@@ -2846,11 +2849,11 @@
         <v>6</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
-      <c r="L18" s="83"/>
+      <c r="L18" s="78"/>
       <c r="M18" s="21"/>
       <c r="O18" t="s">
         <v>58</v>
@@ -2859,7 +2862,7 @@
         <v>29</v>
       </c>
       <c r="R18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S18" t="s">
         <v>59</v>
@@ -2867,6 +2870,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="I11:I12"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="L2:L4"/>
@@ -2883,11 +2891,6 @@
     <mergeCell ref="B5:B10"/>
     <mergeCell ref="C5:C10"/>
     <mergeCell ref="D5:D10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="I11:I12"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O18" xr:uid="{0E9AAD0A-3D19-48F8-A102-B971FC4B1A2B}">
@@ -2964,16 +2967,16 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="45.75">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="79">
+      <c r="D2" s="83">
         <v>896583</v>
       </c>
       <c r="E2" s="7" t="s">
@@ -2993,10 +2996,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="121.5">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="79"/>
+      <c r="A3" s="84"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="83"/>
       <c r="E3" s="7" t="s">
         <v>30</v>
       </c>
@@ -3014,10 +3017,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="60.75">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="79"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="83"/>
       <c r="E4" s="7" t="str">
         <f>E2</f>
         <v xml:space="preserve">Policy or Regulatory Framework and pilot activities </v>
@@ -3036,14 +3039,14 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="45.75" customHeight="1">
-      <c r="A5" s="78">
+      <c r="A5" s="80">
         <v>1061012</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="91">
+      <c r="C5" s="87"/>
+      <c r="D5" s="88">
         <v>1128978</v>
       </c>
       <c r="E5" s="27" t="s">
@@ -3063,10 +3066,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="70.5" customHeight="1">
-      <c r="A6" s="78"/>
-      <c r="B6" s="88"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="91"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="85"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="88"/>
       <c r="E6" s="27" t="s">
         <v>46</v>
       </c>
@@ -3084,10 +3087,10 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="45.75">
-      <c r="A7" s="78"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="91"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="88"/>
       <c r="E7" s="27" t="s">
         <v>46</v>
       </c>
@@ -3105,10 +3108,10 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="30.75">
-      <c r="A8" s="78"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="91"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="27" t="s">
         <v>90</v>
       </c>
@@ -3126,10 +3129,10 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="50.25">
-      <c r="A9" s="78"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="91"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="88"/>
       <c r="E9" s="7" t="s">
         <v>30</v>
       </c>
@@ -3147,10 +3150,10 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="37.5">
-      <c r="A10" s="78"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="91"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="88"/>
       <c r="E10" s="27" t="str">
         <f>'Beneficiary Categories'!B15</f>
         <v>Policy or Regulatory Framework</v>
@@ -3169,16 +3172,16 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="5" customFormat="1" ht="161.25" customHeight="1">
-      <c r="A11" s="76">
+      <c r="A11" s="89">
         <v>134019</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="79">
+      <c r="D11" s="83">
         <v>3000000</v>
       </c>
       <c r="E11" s="10" t="s">
@@ -3193,20 +3196,20 @@
       <c r="H11" s="8">
         <v>70</v>
       </c>
-      <c r="I11" s="80" t="s">
+      <c r="I11" s="91" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="6" customFormat="1" ht="91.5">
-      <c r="A12" s="76"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="79"/>
+      <c r="A12" s="89"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="83"/>
       <c r="E12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="19" t="s">
         <v>60</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="20">
         <v>0</v>
@@ -3214,19 +3217,19 @@
       <c r="H12" s="20">
         <v>20</v>
       </c>
-      <c r="I12" s="80"/>
+      <c r="I12" s="91"/>
     </row>
     <row r="13" spans="1:10" ht="183" customHeight="1">
-      <c r="A13" s="84">
+      <c r="A13" s="79">
         <v>117633</v>
       </c>
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="86" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="79">
+      <c r="D13" s="83">
         <v>2201100</v>
       </c>
       <c r="E13" s="21" t="s">
@@ -3242,19 +3245,19 @@
         <v>93</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="168" customHeight="1">
-      <c r="A14" s="78"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="79"/>
+      <c r="A14" s="80"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="83"/>
       <c r="E14" s="21" t="s">
         <v>94</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" s="13">
         <v>0</v>
@@ -3267,15 +3270,15 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="30.75">
-      <c r="A15" s="78"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="79"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="83"/>
       <c r="E15" s="21" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
@@ -3284,14 +3287,14 @@
         <v>3</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="76.5">
-      <c r="A16" s="78"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="79"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="83"/>
       <c r="E16" s="21" t="s">
         <v>79</v>
       </c>
@@ -3305,19 +3308,19 @@
         <v>98</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="76.5">
-      <c r="A17" s="78"/>
-      <c r="B17" s="85"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="79"/>
+      <c r="A17" s="80"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="83"/>
       <c r="E17" s="21" t="s">
         <v>79</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
@@ -3326,14 +3329,14 @@
         <v>46</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="121.5">
-      <c r="A18" s="78"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="79"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="83"/>
       <c r="E18" s="21" t="s">
         <v>80</v>
       </c>
@@ -3347,19 +3350,11 @@
         <v>6</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A10"/>
-    <mergeCell ref="B5:B10"/>
-    <mergeCell ref="C5:C10"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
     <mergeCell ref="C13:C18"/>
     <mergeCell ref="D13:D18"/>
     <mergeCell ref="B13:B18"/>
@@ -3369,6 +3364,14 @@
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A10"/>
+    <mergeCell ref="B5:B10"/>
+    <mergeCell ref="C5:C10"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C13" r:id="rId1" xr:uid="{D6EF8A47-5441-4CF6-A2B7-731F05227061}"/>
@@ -3432,7 +3435,7 @@
         <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>105</v>
@@ -3479,7 +3482,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>113</v>
@@ -3488,7 +3491,7 @@
     <row r="11" spans="1:3">
       <c r="A11" s="94"/>
       <c r="B11" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>114</v>
@@ -3508,7 +3511,7 @@
     <row r="13" spans="1:3">
       <c r="A13" s="95"/>
       <c r="B13" s="4" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>116</v>
@@ -3557,26 +3560,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3825,8 +3808,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2295D2-686C-4E88-AC90-9CDCBA3A093B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{026D64B1-7D69-471C-86B7-14AEDFA13599}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3834,5 +3837,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{026D64B1-7D69-471C-86B7-14AEDFA13599}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2295D2-686C-4E88-AC90-9CDCBA3A093B}"/>
 </file>
--- a/01_Input/00_CO Validation/Viet Nam - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Viet Nam - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="623" documentId="11_D8F61223F3A0F98994E878555E7F6C80D2E00C80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC18741B-D8C3-4DBC-AF91-B2DDB704445F}"/>
+  <xr:revisionPtr revIDLastSave="626" documentId="11_D8F61223F3A0F98994E878555E7F6C80D2E00C80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50684D2E-1A8B-4BF2-A639-1543FE4905D7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="136">
   <si>
     <t>Project ID</t>
   </si>
@@ -110,7 +110,7 @@
     <t>https://www.undp.org/vietnam/projects/catalysing-sustainable-shift-towards-e-mobility</t>
   </si>
   <si>
-    <t>GHG Emission Reduction</t>
+    <t>GHG Emissions Reduction</t>
   </si>
   <si>
     <t xml:space="preserve">Tons of CO2 emissions avoided or reduced/year 
@@ -184,10 +184,6 @@
   </si>
   <si>
     <t>National</t>
-  </si>
-  <si>
-    <t>should we add 6 as final results in the Target column? 
--&gt; Please feel free to revise. I myself think that we should have another column on Achievements.</t>
   </si>
   <si>
     <t>Scaling up E-mobility and mechanisms for promoting investments in green projects in Viet Nam (March 2023 - March 2024</t>
@@ -315,6 +311,83 @@
     <t>Solar</t>
   </si>
   <si>
+    <t>Agriculture and Food System</t>
+  </si>
+  <si>
+    <t>Agricultural Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 100  households, corresponding to 300 farmers benefitted from the project support to shrimp and dragron fruit models at two provinces Binh Thuan and Bac Lieu; and 1,000 turns of people at provincial, district and commune levels benefitted from project trainings </t>
+  </si>
+  <si>
+    <t>Small Enterprises</t>
+  </si>
+  <si>
+    <t>03 Small businesses/cooperatives improved marketting and green labelling via e-commerce/online practices</t>
+  </si>
+  <si>
+    <t>Capacity Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - nearly 1000 local farmers/producers received trainign on sustainable shrimp farming, green technology application etc. 
+- Nearly 600 local farmers/producers received  trainign on sustainable dragon fruit farming, green technology application, e-commerce, carbon footprint tracking</t>
+  </si>
+  <si>
+    <t># of firms</t>
+  </si>
+  <si>
+    <t>4 firms/cooperatives in Binh Thuan and 2 cooperatives in Bac Lieu received full training packages for full green transformation process
+At least 40 local firms/cooperatives in two provices received different topical training on green technologies, e-commerce, green treacebility/carbon footprint tracking, Global gap/vietgap, etc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Update Viet Nam NDC update 2022
+- Develop Viet Nam NDCC 2022
+- 01 completed proposal for direct lending modality for Small and Medium Enterprise Fund
+- 01 Climate Business Index Platform
+- 2 Agriculture supply chain and apps platform for green dragon fruits and green shrimp (on-going)
+</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>00130633</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Policy and Regulatory Frameworks</t>
+  </si>
+  <si>
+    <t>should we add 6 as final results in the Target column? 
+-&gt; Please feel free to revise. I myself think that we should have another column on Achievements.</t>
+  </si>
+  <si>
+    <t>Incentives and Support</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
+  </si>
+  <si>
+    <t>50 kW</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -342,15 +415,6 @@
     </r>
   </si>
   <si>
-    <t>Agriculture and Food System</t>
-  </si>
-  <si>
-    <t>Agricultural Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 100  households, corresponding to 300 farmers benefitted from the project support to shrimp and dragron fruit models at two provinces Binh Thuan and Bac Lieu; and 1,000 turns of people at provincial, district and commune levels benefitted from project trainings </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -368,73 +432,6 @@
       </rPr>
       <t>-&gt; Revised.</t>
     </r>
-  </si>
-  <si>
-    <t>Small Enterprises</t>
-  </si>
-  <si>
-    <t>03 Small businesses/cooperatives improved marketting and green labelling via e-commerce/online practices</t>
-  </si>
-  <si>
-    <t>Capacity Training</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - nearly 1000 local farmers/producers received trainign on sustainable shrimp farming, green technology application etc. 
-- Nearly 600 local farmers/producers received  trainign on sustainable dragon fruit farming, green technology application, e-commerce, carbon footprint tracking</t>
-  </si>
-  <si>
-    <t># of firms</t>
-  </si>
-  <si>
-    <t>4 firms/cooperatives in Binh Thuan and 2 cooperatives in Bac Lieu received full training packages for full green transformation process
-At least 40 local firms/cooperatives in two provices received different topical training on green technologies, e-commerce, green treacebility/carbon footprint tracking, Global gap/vietgap, etc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Update Viet Nam NDC update 2022
-- Develop Viet Nam NDCC 2022
-- 01 completed proposal for direct lending modality for Small and Medium Enterprise Fund
-- 01 Climate Business Index Platform
-- 2 Agriculture supply chain and apps platform for green dragon fruits and green shrimp (on-going)
-</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>00130633</t>
-  </si>
-  <si>
-    <t>GHG Emissions Reduction</t>
-  </si>
-  <si>
-    <t>Energy Efficiency</t>
-  </si>
-  <si>
-    <t>Policy and Regulatory Frameworks</t>
-  </si>
-  <si>
-    <t>Incentives and Support</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Other Energy Services</t>
-  </si>
-  <si>
-    <t>Entrepreneurship Training</t>
-  </si>
-  <si>
-    <t>Scale up energy finance</t>
-  </si>
-  <si>
-    <t>50 kW</t>
   </si>
   <si>
     <t>Capacity Building</t>
@@ -874,7 +871,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -982,9 +979,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1076,9 +1070,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1471,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874F726E-0702-4819-A4CE-990D59EFF568}">
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
@@ -1496,85 +1487,85 @@
     <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30.75">
-      <c r="A1" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68" t="s">
+    <row r="1" spans="1:21" ht="30.75">
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="69" t="s">
+      <c r="J1" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="69" t="s">
+      <c r="K1" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="75" t="s">
+      <c r="L1" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="76" t="s">
+      <c r="M1" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="75" t="s">
+      <c r="N1" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="75" t="s">
+      <c r="O1" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="76" t="s">
+      <c r="P1" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="76" t="s">
+      <c r="Q1" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="77" t="s">
+      <c r="R1" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="78" t="s">
+      <c r="S1" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="77" t="s">
+      <c r="T1" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="78" t="s">
+      <c r="U1" s="76" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="45.75" customHeight="1">
-      <c r="A2" s="44">
+    <row r="2" spans="1:21" ht="45.75" customHeight="1">
+      <c r="A2" s="43">
         <v>130633</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="46">
         <v>896583</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -1589,34 +1580,30 @@
       <c r="I2" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="48"/>
-      <c r="L2" s="79" t="s">
+      <c r="K2" s="47"/>
+      <c r="L2" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="72"/>
-      <c r="N2" s="80" t="s">
+      <c r="M2" s="70"/>
+      <c r="N2" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="81"/>
-      <c r="W2" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="X2" s="3"/>
-    </row>
-    <row r="3" spans="1:24" ht="121.5">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="79"/>
+    </row>
+    <row r="3" spans="1:21" ht="121.5">
+      <c r="A3" s="48"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="E3" s="3" t="s">
         <v>29</v>
       </c>
@@ -1632,34 +1619,30 @@
       <c r="I3" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="48" t="s">
+      <c r="J3" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="53"/>
-      <c r="L3" s="79" t="s">
+      <c r="K3" s="52"/>
+      <c r="L3" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="72"/>
-      <c r="N3" s="80" t="s">
+      <c r="M3" s="70"/>
+      <c r="N3" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="81"/>
-      <c r="W3" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="X3" s="3"/>
-    </row>
-    <row r="4" spans="1:24" ht="305.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="57"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="70"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="70"/>
+      <c r="U3" s="79"/>
+    </row>
+    <row r="4" spans="1:21" ht="259.5">
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="56"/>
       <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
@@ -1675,55 +1658,49 @@
       <c r="I4" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="48" t="s">
+      <c r="J4" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="58"/>
-      <c r="L4" s="79" t="s">
+      <c r="K4" s="57"/>
+      <c r="L4" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="72"/>
-      <c r="N4" s="80" t="s">
+      <c r="M4" s="70"/>
+      <c r="N4" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="72" t="s">
+      <c r="O4" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72" t="s">
+      <c r="P4" s="70"/>
+      <c r="Q4" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="R4" s="72" t="s">
+      <c r="R4" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="81"/>
-      <c r="T4" s="72" t="s">
+      <c r="S4" s="79"/>
+      <c r="T4" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="U4" s="81"/>
-      <c r="W4" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="X4" s="39" t="s">
+      <c r="U4" s="79"/>
+    </row>
+    <row r="5" spans="1:21" ht="90.75" customHeight="1">
+      <c r="A5" s="47">
+        <v>1061012</v>
+      </c>
+      <c r="B5" s="44" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" ht="90.75" customHeight="1">
-      <c r="A5" s="48">
-        <v>1061012</v>
-      </c>
-      <c r="B5" s="45" t="s">
+      <c r="C5" s="47"/>
+      <c r="D5" s="46">
+        <v>1128978</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C5" s="48"/>
-      <c r="D5" s="47">
-        <v>1128978</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -1732,37 +1709,35 @@
         <v>45</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="79" t="s">
+      <c r="L5" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="72"/>
-      <c r="N5" s="80" t="s">
+      <c r="M5" s="70"/>
+      <c r="N5" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="72"/>
-      <c r="U5" s="81"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-    </row>
-    <row r="6" spans="1:24" ht="70.5" customHeight="1">
-      <c r="A6" s="53"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="59"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="70"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="70"/>
+      <c r="U5" s="79"/>
+    </row>
+    <row r="6" spans="1:21" ht="70.5" customHeight="1">
+      <c r="A6" s="52"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -1771,80 +1746,76 @@
         <v>4.2</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="79" t="s">
+      <c r="L6" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="72"/>
-      <c r="N6" s="80" t="s">
+      <c r="M6" s="70"/>
+      <c r="N6" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="81" t="s">
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="79" t="s">
+        <v>43</v>
+      </c>
+      <c r="T6" s="70"/>
+      <c r="U6" s="79"/>
+    </row>
+    <row r="7" spans="1:21" ht="45.75">
+      <c r="A7" s="52"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="T6" s="72"/>
-      <c r="U6" s="81"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-    </row>
-    <row r="7" spans="1:24" ht="45.75">
-      <c r="A7" s="53"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="23" t="s">
+      <c r="F7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="39">
         <v>570</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="79" t="s">
+      <c r="L7" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="72"/>
-      <c r="N7" s="80" t="s">
+      <c r="M7" s="70"/>
+      <c r="N7" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="72"/>
-      <c r="S7" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="T7" s="72"/>
-      <c r="U7" s="81"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-    </row>
-    <row r="8" spans="1:24" ht="45.75">
-      <c r="A8" s="53"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="59"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="79" t="s">
+        <v>43</v>
+      </c>
+      <c r="T7" s="70"/>
+      <c r="U7" s="79"/>
+    </row>
+    <row r="8" spans="1:21" ht="45.75">
+      <c r="A8" s="52"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="58"/>
       <c r="E8" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="40" t="s">
         <v>47</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>48</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -1853,37 +1824,35 @@
         <v>70</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="79" t="s">
+      <c r="L8" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M8" s="72"/>
-      <c r="N8" s="80" t="s">
+      <c r="M8" s="70"/>
+      <c r="N8" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="81"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-    </row>
-    <row r="9" spans="1:24" ht="50.25">
-      <c r="A9" s="53"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="59"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
+      <c r="Q8" s="70"/>
+      <c r="R8" s="70"/>
+      <c r="S8" s="79"/>
+      <c r="T8" s="70"/>
+      <c r="U8" s="79"/>
+    </row>
+    <row r="9" spans="1:21" ht="50.25">
+      <c r="A9" s="52"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="58"/>
       <c r="E9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="41" t="s">
-        <v>49</v>
+      <c r="F9" s="40" t="s">
+        <v>48</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -1892,38 +1861,36 @@
         <v>370</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="79" t="s">
+      <c r="L9" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M9" s="72"/>
-      <c r="N9" s="80" t="s">
+      <c r="M9" s="70"/>
+      <c r="N9" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="81"/>
-      <c r="T9" s="72"/>
-      <c r="U9" s="81"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-    </row>
-    <row r="10" spans="1:24" ht="45.75">
-      <c r="A10" s="58"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="60"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="70"/>
+      <c r="R9" s="70"/>
+      <c r="S9" s="79"/>
+      <c r="T9" s="70"/>
+      <c r="U9" s="79"/>
+    </row>
+    <row r="10" spans="1:21" ht="45.75">
+      <c r="A10" s="57"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="59"/>
       <c r="E10" s="23" t="str">
         <f>'Beneficiary Categories'!A15</f>
         <v>Medium Enterprises</v>
       </c>
-      <c r="F10" s="42" t="s">
-        <v>50</v>
+      <c r="F10" s="41" t="s">
+        <v>49</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -1932,45 +1899,43 @@
         <v>4</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="79" t="s">
+      <c r="L10" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="72"/>
-      <c r="N10" s="80" t="s">
+      <c r="M10" s="70"/>
+      <c r="N10" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="81"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-    </row>
-    <row r="11" spans="1:24" s="1" customFormat="1" ht="161.25" customHeight="1">
-      <c r="A11" s="61">
+      <c r="O10" s="70"/>
+      <c r="P10" s="70"/>
+      <c r="Q10" s="70"/>
+      <c r="R10" s="70"/>
+      <c r="S10" s="79"/>
+      <c r="T10" s="70"/>
+      <c r="U10" s="79"/>
+    </row>
+    <row r="11" spans="1:21" s="1" customFormat="1" ht="161.25" customHeight="1">
+      <c r="A11" s="60">
         <v>134019</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="D11" s="46">
+        <v>3000000</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="47">
-        <v>3000000</v>
-      </c>
-      <c r="E11" s="23" t="s">
+      <c r="F11" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -1978,38 +1943,36 @@
       <c r="H11" s="5">
         <v>70</v>
       </c>
-      <c r="I11" s="62" t="s">
-        <v>55</v>
+      <c r="I11" s="61" t="s">
+        <v>54</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
-      <c r="L11" s="79" t="s">
+      <c r="L11" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M11" s="72"/>
-      <c r="N11" s="80" t="s">
+      <c r="M11" s="70"/>
+      <c r="N11" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="81"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-    </row>
-    <row r="12" spans="1:24" s="2" customFormat="1" ht="91.5">
-      <c r="A12" s="63"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="57"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="70"/>
+      <c r="U11" s="79"/>
+    </row>
+    <row r="12" spans="1:21" s="2" customFormat="1" ht="91.5">
+      <c r="A12" s="62"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="5">
         <v>0</v>
@@ -2017,44 +1980,42 @@
       <c r="H12" s="5">
         <v>20</v>
       </c>
-      <c r="I12" s="64"/>
+      <c r="I12" s="63"/>
       <c r="J12" s="35"/>
       <c r="K12" s="35"/>
-      <c r="L12" s="79" t="s">
+      <c r="L12" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M12" s="72"/>
-      <c r="N12" s="80" t="s">
+      <c r="M12" s="70"/>
+      <c r="N12" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="72"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="72"/>
-      <c r="U12" s="81"/>
-      <c r="W12" s="35"/>
-      <c r="X12" s="35"/>
-    </row>
-    <row r="13" spans="1:24" ht="183" customHeight="1">
-      <c r="A13" s="44">
+      <c r="O12" s="70"/>
+      <c r="P12" s="70"/>
+      <c r="Q12" s="70"/>
+      <c r="R12" s="70"/>
+      <c r="S12" s="79"/>
+      <c r="T12" s="70"/>
+      <c r="U12" s="79"/>
+    </row>
+    <row r="13" spans="1:21" ht="183" customHeight="1">
+      <c r="A13" s="43">
         <v>117633</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="65" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="47">
+      <c r="D13" s="46">
         <v>2201100</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" s="5">
         <v>0</v>
@@ -2063,43 +2024,37 @@
         <v>0.05</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="79" t="s">
+      <c r="L13" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M13" s="72"/>
-      <c r="N13" s="80" t="s">
+      <c r="M13" s="70"/>
+      <c r="N13" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="81" t="s">
+      <c r="O13" s="70"/>
+      <c r="P13" s="70"/>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="70"/>
+      <c r="S13" s="79" t="s">
+        <v>59</v>
+      </c>
+      <c r="T13" s="70"/>
+      <c r="U13" s="79"/>
+    </row>
+    <row r="14" spans="1:21" ht="168" customHeight="1">
+      <c r="A14" s="48"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T13" s="72"/>
-      <c r="U13" s="81"/>
-      <c r="W13" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="X13" s="33" t="s">
+      <c r="F14" s="3" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="168" customHeight="1">
-      <c r="A14" s="49"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="G14" s="5">
         <v>0</v>
@@ -2107,42 +2062,36 @@
       <c r="H14" s="5">
         <v>1300</v>
       </c>
-      <c r="I14" s="43" t="s">
-        <v>64</v>
+      <c r="I14" s="42" t="s">
+        <v>62</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="79" t="s">
+      <c r="L14" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M14" s="72"/>
-      <c r="N14" s="80" t="s">
+      <c r="M14" s="70"/>
+      <c r="N14" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="72"/>
-      <c r="U14" s="81"/>
-      <c r="W14" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="X14" s="37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="45.75">
-      <c r="A15" s="49"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="52"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="70"/>
+      <c r="Q14" s="70"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="79"/>
+      <c r="T14" s="70"/>
+      <c r="U14" s="79"/>
+    </row>
+    <row r="15" spans="1:21" ht="45.75">
+      <c r="A15" s="48"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G15" s="5">
         <v>0</v>
@@ -2151,39 +2100,35 @@
         <v>3</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="79" t="s">
+      <c r="L15" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M15" s="72"/>
-      <c r="N15" s="80" t="s">
+      <c r="M15" s="70"/>
+      <c r="N15" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O15" s="72"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="81"/>
-      <c r="T15" s="72"/>
-      <c r="U15" s="81"/>
-      <c r="W15" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="X15" s="3"/>
-    </row>
-    <row r="16" spans="1:24" ht="76.5">
-      <c r="A16" s="49"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="52"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
+      <c r="S15" s="79"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="79"/>
+    </row>
+    <row r="16" spans="1:21" ht="76.5">
+      <c r="A16" s="48"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G16" s="5">
         <v>0</v>
@@ -2191,40 +2136,36 @@
       <c r="H16" s="5">
         <v>1600</v>
       </c>
-      <c r="I16" s="43" t="s">
-        <v>69</v>
+      <c r="I16" s="42" t="s">
+        <v>66</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="79" t="s">
+      <c r="L16" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M16" s="72"/>
-      <c r="N16" s="80" t="s">
+      <c r="M16" s="70"/>
+      <c r="N16" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O16" s="72"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="72"/>
-      <c r="U16" s="81"/>
-      <c r="W16" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="1:24" ht="76.5">
-      <c r="A17" s="49"/>
-      <c r="B17" s="53"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="52"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
+      <c r="S16" s="79"/>
+      <c r="T16" s="70"/>
+      <c r="U16" s="79"/>
+    </row>
+    <row r="17" spans="1:21" ht="76.5">
+      <c r="A17" s="48"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G17" s="5">
         <v>0</v>
@@ -2233,34 +2174,30 @@
         <v>46</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="79" t="s">
+      <c r="L17" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="72"/>
-      <c r="N17" s="80" t="s">
+      <c r="M17" s="70"/>
+      <c r="N17" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O17" s="72"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="81"/>
-      <c r="T17" s="72"/>
-      <c r="U17" s="81"/>
-      <c r="W17" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="X17" s="3"/>
-    </row>
-    <row r="18" spans="1:24" ht="121.5">
-      <c r="A18" s="54"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="57"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="79"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="79"/>
+    </row>
+    <row r="18" spans="1:21" ht="121.5">
+      <c r="A18" s="53"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="56"/>
       <c r="E18" s="3" t="s">
         <v>19</v>
       </c>
@@ -2273,37 +2210,33 @@
       <c r="H18" s="5">
         <v>6</v>
       </c>
-      <c r="I18" s="43" t="s">
-        <v>72</v>
+      <c r="I18" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="70"/>
-      <c r="L18" s="79" t="s">
+      <c r="K18" s="69"/>
+      <c r="L18" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M18" s="72"/>
-      <c r="N18" s="80" t="s">
+      <c r="M18" s="70"/>
+      <c r="N18" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="O18" s="72" t="s">
+      <c r="O18" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72" t="s">
+      <c r="P18" s="70"/>
+      <c r="Q18" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="R18" s="72" t="s">
+      <c r="R18" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="S18" s="81"/>
-      <c r="T18" s="72" t="s">
+      <c r="S18" s="79"/>
+      <c r="T18" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="U18" s="81"/>
-      <c r="W18" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="X18" s="71"/>
+      <c r="U18" s="79"/>
     </row>
   </sheetData>
   <dataValidations count="9">
@@ -2413,10 +2346,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>13</v>
@@ -2435,20 +2368,20 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="45.75">
-      <c r="A2" s="93" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="94" t="s">
+      <c r="A2" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="85">
+      <c r="D2" s="83">
         <v>896583</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>24</v>
@@ -2462,11 +2395,11 @@
       <c r="I2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="87" t="s">
+      <c r="J2" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87" t="s">
+      <c r="K2" s="85"/>
+      <c r="L2" s="85" t="s">
         <v>27</v>
       </c>
       <c r="M2" s="17"/>
@@ -2474,16 +2407,16 @@
         <v>28</v>
       </c>
       <c r="P2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="121.5">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="85"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="83"/>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>30</v>
@@ -2497,18 +2430,18 @@
       <c r="I3" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
       <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:19" ht="259.5">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="85"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="83"/>
       <c r="E4" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>32</v>
@@ -2522,41 +2455,41 @@
       <c r="I4" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
       <c r="M4" s="36" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
       </c>
       <c r="P4" t="s">
+        <v>73</v>
+      </c>
+      <c r="R4" t="s">
+        <v>76</v>
+      </c>
+      <c r="S4" t="s">
         <v>77</v>
       </c>
-      <c r="R4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S4" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="5" spans="1:19" ht="45.75" customHeight="1">
-      <c r="A5" s="84">
+      <c r="A5" s="82">
         <v>1061012</v>
       </c>
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="92" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="94"/>
+      <c r="D5" s="95">
+        <v>1128978</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="97">
-        <v>1128978</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="G5" s="9">
         <v>0</v>
@@ -2565,7 +2498,7 @@
         <v>45</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
@@ -2575,19 +2508,19 @@
         <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="70.5" customHeight="1">
-      <c r="A6" s="84"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="97"/>
+      <c r="A6" s="82"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="95"/>
       <c r="E6" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="G6" s="9">
         <v>0</v>
@@ -2596,29 +2529,29 @@
         <v>4.2</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="O6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="45.75">
-      <c r="A7" s="84"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="97"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="95"/>
       <c r="E7" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="G7" s="9">
         <v>0</v>
@@ -2627,7 +2560,7 @@
         <v>570</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
@@ -2637,19 +2570,19 @@
         <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="30.75">
-      <c r="A8" s="84"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="97"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
       <c r="E8" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
@@ -2658,7 +2591,7 @@
         <v>70</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -2666,15 +2599,15 @@
       <c r="M8" s="17"/>
     </row>
     <row r="9" spans="1:19" ht="50.25">
-      <c r="A9" s="84"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="97"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="95"/>
       <c r="E9" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -2683,7 +2616,7 @@
         <v>370</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -2691,16 +2624,16 @@
       <c r="M9" s="17"/>
     </row>
     <row r="10" spans="1:19" ht="37.5">
-      <c r="A10" s="84"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="97"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="95"/>
       <c r="E10" s="23" t="str">
         <f>'Beneficiary Categories'!A15</f>
         <v>Medium Enterprises</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="9">
         <v>0</v>
@@ -2709,7 +2642,7 @@
         <v>4</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
@@ -2719,33 +2652,33 @@
         <v>28</v>
       </c>
       <c r="P10" t="s">
+        <v>73</v>
+      </c>
+      <c r="R10" t="s">
+        <v>76</v>
+      </c>
+      <c r="S10" t="s">
         <v>77</v>
       </c>
-      <c r="R10" t="s">
-        <v>79</v>
-      </c>
-      <c r="S10" t="s">
+    </row>
+    <row r="11" spans="1:19" s="1" customFormat="1" ht="161.25" customHeight="1">
+      <c r="A11" s="80">
+        <v>134019</v>
+      </c>
+      <c r="B11" s="81" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="83">
+        <v>3000000</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" s="1" customFormat="1" ht="161.25" customHeight="1">
-      <c r="A11" s="82">
-        <v>134019</v>
-      </c>
-      <c r="B11" s="83" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="85">
-        <v>3000000</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="F11" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -2753,37 +2686,37 @@
       <c r="H11" s="4">
         <v>70</v>
       </c>
-      <c r="I11" s="86" t="s">
-        <v>55</v>
+      <c r="I11" s="84" t="s">
+        <v>54</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="O11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q11"/>
       <c r="R11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:19" s="2" customFormat="1" ht="91.5">
-      <c r="A12" s="82"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="85"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83"/>
       <c r="E12" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="16">
         <v>0</v>
@@ -2791,78 +2724,78 @@
       <c r="H12" s="16">
         <v>20</v>
       </c>
-      <c r="I12" s="86"/>
+      <c r="I12" s="84"/>
       <c r="J12" s="30"/>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
       <c r="O12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q12"/>
       <c r="R12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="183" customHeight="1">
-      <c r="A13" s="90">
+      <c r="A13" s="88">
         <v>117633</v>
       </c>
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="D13" s="83">
+        <v>2201100</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="D13" s="85">
-        <v>2201100</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
-      <c r="L13" s="87" t="s">
+      <c r="L13" s="85" t="s">
         <v>27</v>
       </c>
       <c r="M13" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="O13" t="s">
+        <v>81</v>
+      </c>
+      <c r="P13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="168" customHeight="1">
+      <c r="A14" s="82"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="O13" t="s">
-        <v>84</v>
-      </c>
-      <c r="P13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="168" customHeight="1">
-      <c r="A14" s="84"/>
-      <c r="B14" s="91"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="17" t="s">
-        <v>63</v>
-      </c>
       <c r="F14" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G14" s="9">
         <v>0</v>
@@ -2871,31 +2804,31 @@
         <v>1300</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="88"/>
+      <c r="L14" s="86"/>
       <c r="M14" s="37" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="O14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="30.75">
-      <c r="A15" s="84"/>
-      <c r="B15" s="91"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="85"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="83"/>
       <c r="E15" s="31" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G15" s="9">
         <v>0</v>
@@ -2904,29 +2837,29 @@
         <v>3</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
-      <c r="L15" s="88"/>
+      <c r="L15" s="86"/>
       <c r="M15" s="17"/>
       <c r="O15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="76.5">
-      <c r="A16" s="84"/>
-      <c r="B16" s="91"/>
-      <c r="C16" s="92"/>
-      <c r="D16" s="85"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="83"/>
       <c r="E16" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G16" s="9">
         <v>0</v>
@@ -2935,29 +2868,29 @@
         <v>1600</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
-      <c r="L16" s="88"/>
+      <c r="L16" s="86"/>
       <c r="M16" s="17"/>
       <c r="O16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="76.5">
-      <c r="A17" s="84"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="85"/>
+      <c r="A17" s="82"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="83"/>
       <c r="E17" s="31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G17" s="9">
         <v>0</v>
@@ -2966,26 +2899,26 @@
         <v>46</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
-      <c r="L17" s="88"/>
+      <c r="L17" s="86"/>
       <c r="M17" s="17"/>
       <c r="O17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="121.5">
-      <c r="A18" s="84"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="85"/>
+      <c r="A18" s="82"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="83"/>
       <c r="E18" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
@@ -2997,17 +2930,17 @@
         <v>6</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="89"/>
+      <c r="L18" s="87"/>
       <c r="M18" s="17"/>
       <c r="O18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="R18" t="s">
         <v>35</v>
@@ -3115,41 +3048,41 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="45.75">
-      <c r="A2" s="93" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="94" t="s">
+      <c r="A2" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="85">
+      <c r="D2" s="83">
         <v>896583</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="121.5">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="85"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="83"/>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>30</v>
@@ -3158,17 +3091,17 @@
         <v>0</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I3" s="24" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="60.75">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="85"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="83"/>
       <c r="E4" s="3" t="str">
         <f>E2</f>
         <v xml:space="preserve">Policy or Regulatory Framework and pilot activities </v>
@@ -3187,84 +3120,84 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="45.75" customHeight="1">
-      <c r="A5" s="84">
+      <c r="A5" s="82">
         <v>1061012</v>
       </c>
-      <c r="B5" s="94" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="97">
+      <c r="B5" s="92" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="94"/>
+      <c r="D5" s="95">
         <v>1128978</v>
       </c>
       <c r="E5" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="9">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="70.5" customHeight="1">
+      <c r="A6" s="82"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="70.5" customHeight="1">
-      <c r="A6" s="84"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="23" t="s">
+      <c r="I6" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="45.75">
+      <c r="A7" s="82"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="45.75">
-      <c r="A7" s="84"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="I7" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30.75">
+      <c r="A8" s="82"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="9">
-        <v>0</v>
-      </c>
-      <c r="H7" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>96</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30.75">
-      <c r="A8" s="84"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>97</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
@@ -3273,19 +3206,19 @@
         <v>70</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="50.25">
-      <c r="A9" s="84"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="97"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="95"/>
       <c r="E9" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -3294,20 +3227,20 @@
         <v>370</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="37.5">
-      <c r="A10" s="84"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="97"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="95"/>
       <c r="E10" s="23" t="str">
         <f>'Beneficiary Categories'!A15</f>
         <v>Medium Enterprises</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="9">
         <v>0</v>
@@ -3316,27 +3249,27 @@
         <v>4</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="161.25" customHeight="1">
-      <c r="A11" s="82">
+      <c r="A11" s="80">
         <v>134019</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="81" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="85">
+      <c r="D11" s="83">
         <v>3000000</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -3344,20 +3277,20 @@
       <c r="H11" s="4">
         <v>70</v>
       </c>
-      <c r="I11" s="86" t="s">
+      <c r="I11" s="84" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="2" customFormat="1" ht="91.5">
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" ht="91.5">
-      <c r="A12" s="82"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>56</v>
       </c>
       <c r="G12" s="16">
         <v>0</v>
@@ -3365,68 +3298,68 @@
       <c r="H12" s="16">
         <v>20</v>
       </c>
-      <c r="I12" s="86"/>
+      <c r="I12" s="84"/>
     </row>
     <row r="13" spans="1:10" ht="183" customHeight="1">
-      <c r="A13" s="90">
+      <c r="A13" s="88">
         <v>117633</v>
       </c>
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="D13" s="83">
+        <v>2201100</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="85">
-        <v>2201100</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="s">
+    </row>
+    <row r="14" spans="1:10" ht="168" customHeight="1">
+      <c r="A14" s="82"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="I13" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="168" customHeight="1">
-      <c r="A14" s="84"/>
-      <c r="B14" s="91"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="17" t="s">
+      <c r="F14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="I14" s="22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30.75">
+      <c r="A15" s="82"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30.75">
-      <c r="A15" s="84"/>
-      <c r="B15" s="91"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>66</v>
       </c>
       <c r="G15" s="9">
         <v>0</v>
@@ -3435,40 +3368,40 @@
         <v>3</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="76.5">
-      <c r="A16" s="84"/>
-      <c r="B16" s="91"/>
-      <c r="C16" s="92"/>
-      <c r="D16" s="85"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="83"/>
       <c r="E16" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G16" s="9">
         <v>0</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="76.5">
-      <c r="A17" s="84"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="85"/>
+      <c r="A17" s="82"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="83"/>
       <c r="E17" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G17" s="9">
         <v>0</v>
@@ -3477,16 +3410,16 @@
         <v>46</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="121.5">
-      <c r="A18" s="84"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="85"/>
+      <c r="A18" s="82"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="83"/>
       <c r="E18" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
@@ -3498,7 +3431,7 @@
         <v>6</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -3539,179 +3472,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="71" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="98" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="74" t="s">
+      <c r="A2" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="72" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="96" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="72" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="98" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="74" t="s">
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="96" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="98" t="s">
+      <c r="B4" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="74" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="96" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="98" t="s">
+      <c r="B5" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="74" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="96" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="72" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="98" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="74" t="s">
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="96" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="98" t="s">
+      <c r="B7" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="74" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="96" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="98" t="s">
+      <c r="B8" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="74" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="96" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="98" t="s">
+      <c r="B9" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="74" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="96" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="98" t="s">
+      <c r="B10" s="97" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="99" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="96" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="98" t="s">
+      <c r="B11" s="97" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="99" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="96" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="98" t="s">
+      <c r="B12" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="74" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="96" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="97" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="98" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="99" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="96" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="98" t="s">
+      <c r="B14" s="97" t="s">
         <v>125</v>
       </c>
-      <c r="B14" s="99" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="96" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="97" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="98" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="99" t="s">
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="96" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="97" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="99" t="s">
+    <row r="17" spans="1:2" ht="30.75">
+      <c r="A17" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="72" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="98" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="74" t="s">
+    <row r="18" spans="1:2" ht="30.75">
+      <c r="A18" s="96" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="97" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="98" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="99" t="s">
+    <row r="19" spans="1:2" ht="76.5">
+      <c r="A19" s="96" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="98" t="s">
+      <c r="B19" s="97" t="s">
         <v>131</v>
       </c>
-      <c r="B19" s="99" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="30.75">
+      <c r="A20" s="96" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="98" t="s">
+      <c r="B20" s="97" t="s">
         <v>133</v>
       </c>
-      <c r="B20" s="99" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="45.75">
+      <c r="A21" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="98" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="98" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="100" t="s">
+    <row r="22" spans="1:2" ht="30.75">
+      <c r="A22" s="96" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="97" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="98" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="99" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3720,8 +3653,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3746,6 +3699,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3825,6 +3779,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3968,34 +3927,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{026D64B1-7D69-471C-86B7-14AEDFA13599}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2295D2-686C-4E88-AC90-9CDCBA3A093B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2295D2-686C-4E88-AC90-9CDCBA3A093B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{242C6A4E-D5F7-40A6-BE63-872510DEAD3D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{242C6A4E-D5F7-40A6-BE63-872510DEAD3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9EA5A6B-4907-41A1-A8C7-9BE3F53C78B4}"/>
 </file>
--- a/01_Input/00_CO Validation/Viet Nam - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Viet Nam - Energy Projects.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="626" documentId="11_D8F61223F3A0F98994E878555E7F6C80D2E00C80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50684D2E-1A8B-4BF2-A639-1543FE4905D7}"/>
+  <xr:revisionPtr revIDLastSave="894" documentId="11_D8F61223F3A0F98994E878555E7F6C80D2E00C80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C287678E-1D17-42D8-B045-074D0D895237}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
-    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
+    <sheet name="Projects (4)" sheetId="6" r:id="rId1"/>
+    <sheet name="Projects (3)" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="In-progress Projects 2024 " sheetId="5" state="hidden" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId5"/>
+    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="186">
   <si>
     <t>Project ID</t>
   </si>
@@ -117,22 +119,326 @@
 </t>
   </si>
   <si>
+    <t>262 tCO2e/year from operation of 06 e-garbage truck and 185 e-motorycles</t>
+  </si>
+  <si>
+    <t>Gov. of Japan</t>
+  </si>
+  <si>
+    <t>Non-VF</t>
+  </si>
+  <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Capacity Training</t>
+  </si>
+  <si>
+    <t>Number of people trained/educated/informed and engaged through technical transfers, policy dialogues, workshops, campaigns, and other efforts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result: Direct beneficiaries: 1,127; Indirect beneficiaries: 83,221
+107 people attended national policy dialogues;
+577 people attended techncial workshops 
+1400 students got direct benefits and 30,100 indirect benefits from green transport debate; 
+165 Govt officers, academic, private sectors participated in trainings;
+ 110 participant attended E-bike cycling: 
+185 people borrowed loan to buy E-vehicle </t>
+  </si>
+  <si>
+    <t>Policy and Regulatory Frameworks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of development or sectoral policies/plans/budgets that integrate NDC targets or net-zero goals </t>
+  </si>
+  <si>
+    <t>Results (08 supported policies)
+- Action plan for green energy transition and reduction of carbon dioxide and methane emissions of transport sector (Decision No. 876.QD-TTg) in July 2022;
+'- Technical standard: TCVN 7447-7-722:2023 (IEC 60364-7-722:2018)
+Low voltage electrical installations – Part 7-722: Requirements for special installations or locations – Supplies for electric vehicles
+'- Technical standard: TCVN 13078-25:2023 (IEC 61851-25:2020);
+ Electric vehicle conductive charging system – Part 25: DC EV supply equipment where protection relies on electrical separation
+'-Technical standard: TCVN 13724-7:2023 (IEC 61439-7:2022);
+Low-voltage switchgear and control gear assemblies –Part 7: Assemblies for specific applications such as marinas, camping sites, market squares, electric vehicle charging stations;
+ - National standard on Swappable batteries of electric two-wheel vehicles 
+'- Technical inputs for National Programme on Environmentally Friendly Public Transportation Development;
+'-Technical support for The green transport action plan for Hue city;
+'- Technical input to development of The policy advice paper on E-scooter sharing for last mile connection in Hanoi</t>
+  </si>
+  <si>
+    <t>Incentives and Support</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Scaling up E-mobility and mechanisms for promoting investments in green projects in Viet Nam (March 2023 - March 2024</t>
+  </si>
+  <si>
+    <t>Tonnes of CO2 emissions avoided or reduced/year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6 ton of CO2e  from installed PV solar system 
+Tobe updated, since the result will be calcultated from operation of provided/purchased electric vehicle </t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>Megawatts of renewable or low-emission energy capacity installed, generated or rehabilitated</t>
+  </si>
+  <si>
+    <t>64 Mwh/year</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>Electricity Access</t>
+  </si>
+  <si>
+    <t>Number of beneficiaries with new access to green/sustainable energy</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t>The project is still under the inception phase. So no result is available yet.</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
+    <t>Number of beneficiaries green/sustainable jobs created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228 green/sustainable jobs for people who accessed a loan from project to buy electric motorcycle for delivery or tourism services or drivers of electric garbage trucks
+</t>
+  </si>
+  <si>
+    <t>Number of people trained/educated/informed through technical transfers, dialogues, workshops, campaigns, and other efforts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1292 people trained/educated/informed through technical transfers, dialogues, workshops, campaigns, and other efforts: 657 Male and 635 female  
+</t>
+  </si>
+  <si>
+    <t>Policy and Regulator Frameworks</t>
+  </si>
+  <si>
+    <t>Number of development or sectoral policies/plans/budgets that integrate NDC targets or net-zero goals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 Technical development plan for Road transport 
+02 National technical Standard on battery swapping for 2 wheel vehicle 
+03 technical standard on electric vehicle 
+01 Technical guideline for charging infrastructure of E-Bus 
+01 Renewable energy policy 
+02 Policy on tax and fees for emission of transport vehicle </t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t># of firms</t>
+  </si>
+  <si>
+    <t>06: Selex Motor, HEPCO, Gojex, Grab, Dat Bike, Binh Dinh Environment Joint Stock Company (and to be updated if any)</t>
+  </si>
+  <si>
+    <t>Shifting Investment Flows 
+Towards Green Transformation (SHIFT)</t>
+  </si>
+  <si>
+    <t>N/A yet 
+(Project will be implemented during June 2024 - June 2028)</t>
+  </si>
+  <si>
+    <t>Tonnes of CO2 emissions avoided or reduced/year from two pilots project</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Shifting Investment Flows Towards Green Transformation (SHIFT)’ project in Viet Nam aims at enhancing know-how and capacities of relevant public and private stakeholders in the areas of green finance and energy transition. Joining force with six partners joining to implement SHIFT project, UNDP is responsible for the design and implementation of two work packages. The objective is to generate interest and build technical capacity in the private sector, in particular women-owned enterprises or enterprises with a proven approach to promoting gender equality in RE, EE and energy transition technologies. UNDP will receive EUR 3 million (out of EUR 15 million for the overall project) to implement two work packages: (1) Design and implementation of replicable investment projects in energy transition technologies to substantially reduce greenhouse gas emissions in high energy-consuming sectors; and (2) Catalysing and facilitating the replication and scale-up of the piloted energy transition technologies and other energy transition technologies.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Status:
+- Grant Agreement expected to sign in Q2/2024
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Planned date of attainment: 
+- June 2028
+Notes: 
+- The SHIFT project will be implemented by six organizations.
+- Other standard indicators to be calculated during first interim report.
+Budget: EUR 3000000</t>
+    </r>
+  </si>
+  <si>
+    <t>BMWK/GIZ</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
+  </si>
+  <si>
+    <t>Decarbonization</t>
+  </si>
+  <si>
+    <t>Shifting Investment Flows Towards Green Transformation (SHIFT)’ project in Viet Nam aims at enhancing know-how and capacities of relevant public and private stakeholders in the areas of green finance and energy transition. Joining force with six partners joining to implement SHIFT project, UNDP is responsible for the design and implementation of two work packages. The objective is to generate interest and build technical capacity in the private sector, in particular women-owned enterprises or enterprises with a proven approach to promoting gender equality in RE, EE and energy transition technologies. UNDP will receive EUR 3 million (out of EUR 15 million for the overall project) to implement two work packages: (1) Design and implementation of replicable investment projects in energy transition technologies to substantially reduce greenhouse gas emissions in high energy-consuming sectors; and (2) Catalysing and facilitating the replication and scale-up of the piloted energy transition technologies and other energy transition technologies.</t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
+  </si>
+  <si>
+    <t>Number of enterprises reached by SHIFT's information, dissemination, capacity building and/or technical support confirm they plan to invest in renewable energy, energy efficiency or other energy transition technologies</t>
+  </si>
+  <si>
+    <t>Number of enterprises supported by SHIFT that have implemented technically and financially feasible pilot projects in RE, EE or other energy transition technologies</t>
+  </si>
+  <si>
+    <t>Number of enterprises  that recieved direct financial and and technical supports from SHIFT to invest in RE, EE or other energy transition technologies</t>
+  </si>
+  <si>
+    <t>Accelerating Private Sector Engagement in Climate Resilient and Low Emission Investment Opportunities in Viet Nam’s NDC</t>
+  </si>
+  <si>
+    <t>Accelerating Private Sector Engagement in Climate-Resilient and Low-Emission Investment Opportunities in Viet Nam’s NDC 2019-2023 | United Nations Development Programme (undp.org)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$2'201'100 </t>
+  </si>
+  <si>
+    <t>Completed installation for 60kW in Binh Thuan for 2 Cooperatives/Small Businesses
+02 Agriculture Cooperatives received 6.2x 2 solar-powered drying machines
+Target: 72 kW</t>
+  </si>
+  <si>
+    <t>Agricultural Services</t>
+  </si>
+  <si>
+    <t>367ha</t>
+  </si>
+  <si>
+    <t>- 41.5ha of agriculture land transformed to Energy Efficiency technoligies (application of 9w bulfs for dragon fruit farming instead of 75-100w, saving at least 70-80% energy consumption for dragon fruit production) 
+- 36 ha of agriculture land transformed to irrigation saving technologies
+- 4-5 small businesses/agriculture cooperatives transfered to renewable/energy efficient food processing technologies (on-going until end 2023)
+- 290ha of shrimp farming applied climate resilient and sustainable farming practices</t>
+  </si>
+  <si>
+    <t>Small Enterprises</t>
+  </si>
+  <si>
+    <t>03 Small businesses/cooperatives improved marketting and green labelling via e-commerce/online practices</t>
+  </si>
+  <si>
+    <t>Capacity Building</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - nearly 1000 local farmers/producers received trainign on sustainable shrimp farming, green technology application etc. 
+- Nearly 600 local farmers/producers received  trainign on sustainable dragon fruit farming, green technology application, e-commerce, carbon footprint tracking</t>
+  </si>
+  <si>
+    <t>4 firms/cooperatives in Binh Thuan and 2 cooperatives in Bac Lieu received full training packages for full green transformation process
+At least 40 local firms/cooperatives in two provices received different topical training on green technologies, e-commerce, green treacebility/carbon footprint tracking, Global gap/vietgap, etc</t>
+  </si>
+  <si>
+    <t>- Update Viet Nam NDC update 2022
+- Develop Viet Nam NCCS 2022
+- 01 completed proposal for direct lending modality for Small and Medium Enterprise Fund
+- 01 Climate Business Index Platform
+- 2 Agriculture supply chain and apps platform for green dragon fruits and green shrimp (on-going)
+- 01 Sustainable and Low carbon Dragon Fruit Scheme draft for MARD</t>
+  </si>
+  <si>
+    <t>NDC Support</t>
+  </si>
+  <si>
+    <t>Supporting the Implementation of the Just Energy Transition Partnership (JETP) and Nationally Determined Contribution (NDC) in Viet Nam</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/01000715</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>The Just Energy Transition Partnership (JETP) is a long-term, ambitious partnership to support Viet Nam's low-emission and climate resilient development, as well as to support Viet Nam to accelerate the just transition and decarbonisation of the electricity system, and develop new economic opportunities to support Viet Nam's transition towards net zero future.
+VN Power sector CO2 emissions to peak at 170 Mt in 2030 instead of 240 Mt in 2035.</t>
+  </si>
+  <si>
+    <t>JETP implementation will support Vietnam on implementation of Power Development Plan 8 (PDP8) which aim to increate RE resource to at least 47% of electricity production in 2030.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy reform </t>
+  </si>
+  <si>
+    <t>Number of studies providing policy recommendations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research studies on policy and legal framework to overcome barriers to investment and enhance private sector investment in the energy transition will be included in the JETP-RMP are anticipated to be commissioned with focus on the subjects of (1) financial reforms; (2) coal phasing out (flexibility, repurposing and retirement); renewable energy development, including: (3) OSW power and (4) solar photovoltaics; (5) green hydrogen; (6) renewable energy manufacturing Industry; (7) grid development; (8) storage (battery and pumped hydro); (9) energy efficiency; (10) innovation and technology transfer; and (11) just/social transition. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">High level policy dialogues </t>
+  </si>
+  <si>
+    <t>Number of high-level policy dialogues, stakeholders engagement and consultation meetings</t>
+  </si>
+  <si>
+    <t>Project will provide support to the GOV on the organization of high-level policy dialogues, stakeholder engagement and consultation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There will be large number of people in Vietnam expected to increase awareness and capacity in the topic of energy transition through the JETP website, events organized within the framework of the project. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coal transition </t>
+  </si>
+  <si>
+    <t>Number of CFPP conducted study on GHG inventory and emisison mitigation action plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JETP implementation will support to limit coal power capacity to 30.2 GW by 2030 from a projected 37 GW; 5 Coal-fired Power plants will receive support on developing GHG invesntory report and Emisison mitigation action plans. </t>
+  </si>
+  <si>
+    <t>- Support Vietnam on development of NDC 3.0 
+- Support the development of Domestic carbon market 
+- Support the LULUCF sector on database development for GHG emission reduction potential and measurement of Carbon sequestration for Mangrove Forest. 
+- Support GHG inventory for Coal-fired power plants and support Coal transition in Vietnam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalysing a Sustainable Shift towards E-mobility (March 2022-March 2023) 
+</t>
+  </si>
+  <si>
     <t>To be reported after 1 year of project completion</t>
   </si>
   <si>
-    <t>Gov. of Japan</t>
-  </si>
-  <si>
-    <t>Non-VF</t>
-  </si>
-  <si>
-    <t>Accelerating just energy transition</t>
-  </si>
-  <si>
     <t>Capacity Building Training</t>
-  </si>
-  <si>
-    <t>Number of people trained/educated/informed and engaged through technical transfers, policy dialogues, workshops, campaigns, and other efforts</t>
   </si>
   <si>
     <r>
@@ -151,15 +457,13 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">107 people attended national policy dialogues;
+      <t>107 people attended national policy dialogues;
 1400 students got direct benefits and 30,100 indirect benefits from green transport debate; 
 165 Govt officers, academic, private sectors participated in trainings;
  110 participant attended E-bike cycling: 
-185 people borrowed loan to buy E-vehicle </t>
+185 people borrowed loan to buy E-vehicle 
+Catalysing a Sustainable Shift towards E-Mobility forms part of UNDP’s Climate Promise. The project supports Viet Nam’s targets in its Nationally Determined Contribution (NDC) for the transport sector as well as is aligned with the Ministry of Transport (MOT) Action Programme on Green Transformation and Carbon and Methane Reduction, includes mitigation measures for the transport sector with a focus on modal shift and fuel switch to achieve net zero emission by 2025. The theory of change behind the project is that by promoting and accelerating the shift towards the adoption of EV and clean energy in transport sector will contribute to the achivement of Viet Nam’s targets set in updated NDC. This is done by supporting an enabling environment at both national and city level, delivering capacity building and pilot innovation measures for evidence-based policy formulation, meanwhile raising general public awareness for wider social acceptance.</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of development or sectoral policies/plans/budgets that integrate NDC targets or net-zero goals </t>
   </si>
   <si>
     <t>Results (06 supported policies)
@@ -174,65 +478,26 @@
 '- Technical input to development of The policy advice paper on E-scooter sharing for last mile connection in Hanoi</t>
   </si>
   <si>
-    <t>Renewable Energy</t>
-  </si>
-  <si>
-    <t>NDC Support</t>
-  </si>
-  <si>
-    <t>Decarbonization</t>
-  </si>
-  <si>
     <t>National</t>
   </si>
   <si>
-    <t>Scaling up E-mobility and mechanisms for promoting investments in green projects in Viet Nam (March 2023 - March 2024</t>
-  </si>
-  <si>
-    <t>Tonnes of CO2 emissions avoided or reduced/year</t>
-  </si>
-  <si>
-    <t>The project is still under the inception phase. So no result is available yet.</t>
-  </si>
-  <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
-    <t>Megawatts of renewable or low-emission energy capacity installed, generated or rehabilitated</t>
+    <t>Scaling up E-mobility and mechanisms for promoting investments in green projects in Viet Nam (March 2023 - March 2024)</t>
+  </si>
+  <si>
+    <t>The project is still under the inception phase. So no result is available yet.
+The project supports Viet Nam’s Nationally Determined Contribution (NDC) 2022 targets for the transport sector. Furthermore, the project is aligned with the National Green Growth Strategy for 2021-2030, with a vision to 2050 (approved in Decision No. 1658/QD-TTg), and the Action Programme for Transition to Green Energy and Mitigation of Carbon Dioxide and Methane Emissions from Transportation (approved in Decision No. 876/QD-TTg). Buildup on the achievement of Catalysing a Sustainable Shift towards E-Mobility project to further support the decarbonization of Viet Nam’s transport sector and the development of an eligible carbon market under the Paris Agreement by aiding the establishment of pilot emissions trading markets focused on piloting e-mobility.</t>
   </si>
   <si>
     <t>Unknown</t>
   </si>
   <si>
-    <t>Electricity Access</t>
-  </si>
-  <si>
-    <t>Number of beneficiaries with new access to green/sustainable energy</t>
+    <t>0</t>
   </si>
   <si>
     <t>Other</t>
   </si>
   <si>
-    <t>Number of beneficiaries green/sustainable jobs created</t>
-  </si>
-  <si>
-    <t>Number of people trained/educated/informed through technical transfers, dialogues, workshops, campaigns, and other efforts</t>
-  </si>
-  <si>
-    <t>Number of development or sectoral policies/plans/budgets that integrate NDC targets or net-zero goals</t>
-  </si>
-  <si>
-    <t>Shifting Investment Flows 
-Towards Green Transformation (SHIFT)</t>
-  </si>
-  <si>
     <t>N/A yet</t>
-  </si>
-  <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t>Number of enterprises reached by SHIFT's information, dissemination, capacity building and/or technical support confirm they plan to invest in renewable energy, energy efficiency or other energy transition technologies</t>
   </si>
   <si>
     <r>
@@ -295,13 +560,8 @@
     </r>
   </si>
   <si>
-    <t>Number of enterprises supported by SHIFT that have implemented technically and financially feasible pilot projects in RE, EE or other energy transition technologies</t>
-  </si>
-  <si>
-    <t>Accelerating Private Sector Engagement in Climate Resilient and Low Emission Investment Opportunities in Viet Nam’s NDC</t>
-  </si>
-  <si>
-    <t>Accelerating Private Sector Engagement in Climate-Resilient and Low-Emission Investment Opportunities in Viet Nam’s NDC 2019-2023 | United Nations Development Programme (undp.org)</t>
+    <t xml:space="preserve">
+ </t>
   </si>
   <si>
     <t>Under process for installation for solar rooftop for 13 agriculture cooperatives/small business models in Bac Lieu; 
@@ -314,30 +574,7 @@
     <t>Agriculture and Food System</t>
   </si>
   <si>
-    <t>Agricultural Services</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 100  households, corresponding to 300 farmers benefitted from the project support to shrimp and dragron fruit models at two provinces Binh Thuan and Bac Lieu; and 1,000 turns of people at provincial, district and commune levels benefitted from project trainings </t>
-  </si>
-  <si>
-    <t>Small Enterprises</t>
-  </si>
-  <si>
-    <t>03 Small businesses/cooperatives improved marketting and green labelling via e-commerce/online practices</t>
-  </si>
-  <si>
-    <t>Capacity Training</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - nearly 1000 local farmers/producers received trainign on sustainable shrimp farming, green technology application etc. 
-- Nearly 600 local farmers/producers received  trainign on sustainable dragon fruit farming, green technology application, e-commerce, carbon footprint tracking</t>
-  </si>
-  <si>
-    <t># of firms</t>
-  </si>
-  <si>
-    <t>4 firms/cooperatives in Binh Thuan and 2 cooperatives in Bac Lieu received full training packages for full green transformation process
-At least 40 local firms/cooperatives in two provices received different topical training on green technologies, e-commerce, green treacebility/carbon footprint tracking, Global gap/vietgap, etc</t>
   </si>
   <si>
     <t xml:space="preserve">- Update Viet Nam NDC update 2022
@@ -357,35 +594,181 @@
     <t>00130633</t>
   </si>
   <si>
-    <t>Energy Efficiency</t>
-  </si>
-  <si>
-    <t>Policy and Regulatory Frameworks</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Result: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF31869B"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Direct beneficiaries: 1,127; Indirect beneficiaries: 83,221
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">107 people attended national policy dialogues;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF31869B"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">577 people attended techncial workshops 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">1400 students got direct benefits and 30,100 indirect benefits from green transport debate; 
+165 Govt officers, academic, private sectors participated in trainings;
+ 110 participant attended E-bike cycling: 
+185 people borrowed loan to buy E-vehicle </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Results (08 supported policies)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF31869B"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">- Action plan for green energy transition and reduction of carbon dioxide and methane emissions of transport sector (Decision No. 876.QD-TTg) in July 2022;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>'- Technical standard: TCVN 7447-7-722:2023 (IEC 60364-7-722:2018)
+Low voltage electrical installations – Part 7-722: Requirements for special installations or locations – Supplies for electric vehicles
+'- Technical standard: TCVN 13078-25:2023 (IEC 61851-25:2020);
+ Electric vehicle conductive charging system – Part 25: DC EV supply equipment where protection relies on electrical separation
+'-Technical standard: TCVN 13724-7:2023 (IEC 61439-7:2022);
+Low-voltage switchgear and control gear assemblies –Part 7: Assemblies for specific applications such as marinas, camping sites, market squares, electric vehicle charging stations;
+ -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF31869B"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> National standard on Swappable batteries of electric two-wheel vehicles 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>'- Technical inputs for National Programme on Environmentally Friendly Public Transportation Development;
+'-Technical support for The green transport action plan for Hue city;
+'- Technical input to development of The policy advice paper on E-scooter sharing for last mile connection in Hanoi</t>
+    </r>
   </si>
   <si>
     <t>should we add 6 as final results in the Target column? 
 -&gt; Please feel free to revise. I myself think that we should have another column on Achievements.</t>
   </si>
   <si>
-    <t>Incentives and Support</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Other Energy Services</t>
-  </si>
-  <si>
-    <t>Entrepreneurship Training</t>
-  </si>
-  <si>
-    <t>Scale up energy finance</t>
-  </si>
-  <si>
-    <t>50 kW</t>
+    <t>EUR 3000000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Status:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">- Grant Agreement expected to sign in Q2/2024
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Planned date of attainment:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> 
+- June 2028
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Notes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> 
+- The SHIFT project will be implemented by six organizations.
+- Other standard indicators to be calculated during first interim report.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>72 kW</t>
+  </si>
+  <si>
+    <t>Completed installation for 60kW in Binh Thuan for 2 Cooperatives/Small Businesses
+02 Agriculture Cooperatives received 6.2x 2 solar-powered drying machines</t>
   </si>
   <si>
     <r>
@@ -434,10 +817,41 @@
     </r>
   </si>
   <si>
-    <t>Capacity Building</t>
-  </si>
-  <si>
-    <t>Policy and Regulator Frameworks</t>
+    <t>01000715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VN Power sector CO2 emissions to peak at 170 Mt in 2030 instead of 240 Mt in 2035.
+</t>
+  </si>
+  <si>
+    <t>JETP implementation will support to limit coal power capacity to 30.2 GW by 2030 from a projected 37 GW</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Result:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">107 people attended national policy dialogues;
+1400 students got direct benefits and 30,100 indirect benefits from green transport debate; 
+165 Govt officers, academic, private sectors participated in trainings;
+ 110 participant attended E-bike cycling: 
+185 people borrowed loan to buy E-vehicle </t>
+    </r>
+  </si>
+  <si>
+    <t>50 kW</t>
   </si>
   <si>
     <t xml:space="preserve">Policy or Regulatory Framework and pilot activities </t>
@@ -478,15 +892,6 @@
   </si>
   <si>
     <t>Productive Use of Energy</t>
-  </si>
-  <si>
-    <t>367ha</t>
-  </si>
-  <si>
-    <t>- 41.5ha of agriculture land transformed to Energy Efficiency technoligies (application of 9w bulfs for dragon fruit farming instead of 75-100w, saving at least 70-80% energy consumption for dragon fruit production) 
-- 36 ha of agriculture land transformed to irrigation saving technologies
-- 4-5 small businesses/agriculture cooperatives transfered to renewable/energy efficient food processing technologies (on-going until end 2023)
-- 290ha of shrimp farming applied climate resilient and sustainable farming practices</t>
   </si>
   <si>
     <t>Market Development</t>
@@ -595,15 +1000,22 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -741,8 +1153,98 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF31869B"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF31869B"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -755,8 +1257,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -866,12 +1380,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -888,7 +1413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -903,13 +1428,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -922,10 +1447,10 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -937,55 +1462,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -994,10 +1519,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1009,10 +1534,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1024,10 +1549,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1036,69 +1561,217 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="34" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1106,56 +1779,128 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="6" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1461,8 +2206,1265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C58629E-D480-4B33-B9C6-91B503EDC91C}">
+  <dimension ref="A1:W29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="77.5703125" style="108" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="9" max="9" width="108" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35" customWidth="1"/>
+    <col min="16" max="17" width="22.5703125" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" customWidth="1"/>
+    <col min="20" max="20" width="30" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="82.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" s="101" customFormat="1" ht="30.75">
+      <c r="A1" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="107" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="99" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="99" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="99" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="99" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="100" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="100" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="102" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="102" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="102" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="102" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="103" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="104" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="103" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="104" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+    </row>
+    <row r="2" spans="1:23" s="101" customFormat="1" ht="45.75" customHeight="1">
+      <c r="A2" s="145">
+        <v>130633</v>
+      </c>
+      <c r="B2" s="109" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="143" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="146">
+        <v>896583</v>
+      </c>
+      <c r="E2" s="147" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="148" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="149">
+        <v>0</v>
+      </c>
+      <c r="H2" s="149">
+        <v>50</v>
+      </c>
+      <c r="I2" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="150" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="150"/>
+      <c r="L2" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="150"/>
+      <c r="N2" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="150"/>
+      <c r="Q2" s="150"/>
+      <c r="R2" s="150"/>
+      <c r="S2" s="148"/>
+      <c r="T2" s="150"/>
+      <c r="U2" s="148"/>
+      <c r="V2" s="144"/>
+      <c r="W2" s="144"/>
+    </row>
+    <row r="3" spans="1:23" s="101" customFormat="1" ht="137.25">
+      <c r="A3" s="110"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="152" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="148" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="149">
+        <v>0</v>
+      </c>
+      <c r="H3" s="149">
+        <v>350</v>
+      </c>
+      <c r="I3" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="150" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="150"/>
+      <c r="L3" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="150"/>
+      <c r="N3" s="150"/>
+      <c r="O3" s="150"/>
+      <c r="P3" s="150"/>
+      <c r="Q3" s="150"/>
+      <c r="R3" s="150"/>
+      <c r="S3" s="148"/>
+      <c r="T3" s="150"/>
+      <c r="U3" s="148"/>
+      <c r="V3" s="144"/>
+      <c r="W3" s="144"/>
+    </row>
+    <row r="4" spans="1:23" s="101" customFormat="1" ht="336">
+      <c r="A4" s="153"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="152" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="148" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="149">
+        <v>0</v>
+      </c>
+      <c r="H4" s="114">
+        <v>3</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="150" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="150"/>
+      <c r="N4" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="150"/>
+      <c r="Q4" s="150" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="150" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" s="148"/>
+      <c r="T4" s="150"/>
+      <c r="U4" s="148"/>
+      <c r="V4" s="144"/>
+      <c r="W4" s="144"/>
+    </row>
+    <row r="5" spans="1:23" s="101" customFormat="1" ht="90.75" customHeight="1">
+      <c r="A5" s="154">
+        <v>1061012</v>
+      </c>
+      <c r="B5" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="155"/>
+      <c r="D5" s="146">
+        <v>1128978</v>
+      </c>
+      <c r="E5" s="147" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="148" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="149">
+        <v>0</v>
+      </c>
+      <c r="H5" s="149">
+        <v>45</v>
+      </c>
+      <c r="I5" s="148" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="148"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="150"/>
+      <c r="M5" s="150"/>
+      <c r="N5" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="150"/>
+      <c r="Q5" s="150"/>
+      <c r="R5" s="150"/>
+      <c r="S5" s="148"/>
+      <c r="T5" s="150"/>
+      <c r="U5" s="148"/>
+      <c r="V5" s="144"/>
+      <c r="W5" s="144"/>
+    </row>
+    <row r="6" spans="1:23" s="101" customFormat="1" ht="70.5" customHeight="1">
+      <c r="A6" s="156"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="118" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="148" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="149">
+        <v>0</v>
+      </c>
+      <c r="H6" s="149">
+        <v>4.2</v>
+      </c>
+      <c r="I6" s="148" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="148"/>
+      <c r="K6" s="148"/>
+      <c r="L6" s="150"/>
+      <c r="M6" s="150"/>
+      <c r="N6" s="150" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" s="150" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" s="150"/>
+      <c r="Q6" s="150"/>
+      <c r="R6" s="150"/>
+      <c r="S6" s="148"/>
+      <c r="T6" s="150"/>
+      <c r="U6" s="148"/>
+      <c r="V6" s="144"/>
+      <c r="W6" s="144"/>
+    </row>
+    <row r="7" spans="1:23" s="101" customFormat="1" ht="45.75">
+      <c r="A7" s="156"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="118" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="148" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="149">
+        <v>0</v>
+      </c>
+      <c r="H7" s="158" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="148" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="148"/>
+      <c r="K7" s="148"/>
+      <c r="L7" s="150"/>
+      <c r="M7" s="150"/>
+      <c r="N7" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="P7" s="150"/>
+      <c r="Q7" s="150"/>
+      <c r="R7" s="150"/>
+      <c r="S7" s="148"/>
+      <c r="T7" s="150"/>
+      <c r="U7" s="148"/>
+      <c r="V7" s="144"/>
+      <c r="W7" s="144"/>
+    </row>
+    <row r="8" spans="1:23" s="101" customFormat="1" ht="60.75">
+      <c r="A8" s="156"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="157"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="118" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="116" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="149">
+        <v>0</v>
+      </c>
+      <c r="H8" s="149">
+        <v>70</v>
+      </c>
+      <c r="I8" s="148" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
+      <c r="L8" s="150"/>
+      <c r="M8" s="150"/>
+      <c r="N8" s="150"/>
+      <c r="O8" s="150"/>
+      <c r="P8" s="150"/>
+      <c r="Q8" s="150"/>
+      <c r="R8" s="150"/>
+      <c r="S8" s="148"/>
+      <c r="T8" s="150"/>
+      <c r="U8" s="148"/>
+      <c r="V8" s="144"/>
+      <c r="W8" s="144"/>
+    </row>
+    <row r="9" spans="1:23" s="101" customFormat="1" ht="76.5">
+      <c r="A9" s="156"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="157"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="152" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="116" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="149">
+        <v>0</v>
+      </c>
+      <c r="H9" s="149">
+        <v>370</v>
+      </c>
+      <c r="I9" s="148" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="148"/>
+      <c r="K9" s="148"/>
+      <c r="L9" s="150"/>
+      <c r="M9" s="150"/>
+      <c r="N9" s="150"/>
+      <c r="O9" s="150"/>
+      <c r="P9" s="150"/>
+      <c r="Q9" s="150"/>
+      <c r="R9" s="150"/>
+      <c r="S9" s="148"/>
+      <c r="T9" s="150"/>
+      <c r="U9" s="148"/>
+      <c r="V9" s="144"/>
+      <c r="W9" s="144"/>
+    </row>
+    <row r="10" spans="1:23" s="101" customFormat="1" ht="106.5">
+      <c r="A10" s="156"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="157"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="116" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="149"/>
+      <c r="H10" s="149"/>
+      <c r="I10" s="148" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="148"/>
+      <c r="K10" s="148"/>
+      <c r="L10" s="150"/>
+      <c r="M10" s="150"/>
+      <c r="N10" s="150"/>
+      <c r="O10" s="150"/>
+      <c r="P10" s="150"/>
+      <c r="Q10" s="150"/>
+      <c r="R10" s="150"/>
+      <c r="S10" s="148"/>
+      <c r="T10" s="150"/>
+      <c r="U10" s="148"/>
+      <c r="V10" s="144"/>
+      <c r="W10" s="144"/>
+    </row>
+    <row r="11" spans="1:23" s="105" customFormat="1" ht="161.25" customHeight="1">
+      <c r="A11" s="159"/>
+      <c r="B11" s="159"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="118" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="149">
+        <v>0</v>
+      </c>
+      <c r="H11" s="149">
+        <v>4</v>
+      </c>
+      <c r="I11" s="117" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="160"/>
+      <c r="K11" s="160"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="150"/>
+      <c r="N11" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="O11" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="150"/>
+      <c r="Q11" s="150" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" s="150" t="s">
+        <v>37</v>
+      </c>
+      <c r="S11" s="148"/>
+      <c r="T11" s="150"/>
+      <c r="U11" s="148"/>
+      <c r="V11" s="161"/>
+      <c r="W11" s="161"/>
+    </row>
+    <row r="12" spans="1:23" s="106" customFormat="1" ht="259.5">
+      <c r="A12" s="162">
+        <v>134019</v>
+      </c>
+      <c r="B12" s="162" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="162" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="146">
+        <v>3177276</v>
+      </c>
+      <c r="E12" s="118" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="160" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="149">
+        <v>0</v>
+      </c>
+      <c r="H12" s="149">
+        <v>33000</v>
+      </c>
+      <c r="I12" s="117" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="150" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="150"/>
+      <c r="L12" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="150"/>
+      <c r="N12" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="O12" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" s="150"/>
+      <c r="Q12" s="150" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12" s="150" t="s">
+        <v>67</v>
+      </c>
+      <c r="S12" s="148"/>
+      <c r="T12" s="150"/>
+      <c r="U12" s="148"/>
+      <c r="V12" s="163"/>
+      <c r="W12" s="144" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" s="101" customFormat="1" ht="183" customHeight="1">
+      <c r="A13" s="153"/>
+      <c r="B13" s="156"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="152" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="148" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="149">
+        <v>0</v>
+      </c>
+      <c r="H13" s="114">
+        <v>70</v>
+      </c>
+      <c r="I13" s="148"/>
+      <c r="J13" s="150" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="150"/>
+      <c r="L13" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" s="150"/>
+      <c r="N13" s="150"/>
+      <c r="O13" s="150"/>
+      <c r="P13" s="150"/>
+      <c r="Q13" s="150"/>
+      <c r="R13" s="150"/>
+      <c r="S13" s="148"/>
+      <c r="T13" s="150"/>
+      <c r="U13" s="148"/>
+      <c r="V13" s="144"/>
+      <c r="W13" s="144"/>
+    </row>
+    <row r="14" spans="1:23" s="101" customFormat="1" ht="168" customHeight="1">
+      <c r="A14" s="153"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="152" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="148" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="149">
+        <v>0</v>
+      </c>
+      <c r="H14" s="149">
+        <v>150</v>
+      </c>
+      <c r="I14" s="164"/>
+      <c r="J14" s="150" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="150"/>
+      <c r="L14" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" s="150"/>
+      <c r="N14" s="150"/>
+      <c r="O14" s="150"/>
+      <c r="P14" s="150"/>
+      <c r="Q14" s="150"/>
+      <c r="R14" s="150"/>
+      <c r="S14" s="148"/>
+      <c r="T14" s="150"/>
+      <c r="U14" s="148"/>
+      <c r="V14" s="144"/>
+      <c r="W14" s="144"/>
+    </row>
+    <row r="15" spans="1:23" s="101" customFormat="1" ht="76.5">
+      <c r="A15" s="153"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="118" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="148" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="149">
+        <v>0</v>
+      </c>
+      <c r="H15" s="149">
+        <v>8</v>
+      </c>
+      <c r="I15" s="148"/>
+      <c r="J15" s="150" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" s="150"/>
+      <c r="L15" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" s="150"/>
+      <c r="N15" s="150"/>
+      <c r="O15" s="150"/>
+      <c r="P15" s="150"/>
+      <c r="Q15" s="150"/>
+      <c r="R15" s="150"/>
+      <c r="S15" s="148"/>
+      <c r="T15" s="150"/>
+      <c r="U15" s="148"/>
+      <c r="V15" s="144"/>
+      <c r="W15" s="144"/>
+    </row>
+    <row r="16" spans="1:23" s="101" customFormat="1" ht="60.75">
+      <c r="A16" s="153"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="151"/>
+      <c r="E16" s="152" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="148" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="149">
+        <v>0</v>
+      </c>
+      <c r="H16" s="149">
+        <v>2</v>
+      </c>
+      <c r="I16" s="164"/>
+      <c r="J16" s="150" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" s="150"/>
+      <c r="L16" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="150"/>
+      <c r="N16" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="O16" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16" s="150"/>
+      <c r="Q16" s="150" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" s="150" t="s">
+        <v>67</v>
+      </c>
+      <c r="S16" s="148"/>
+      <c r="T16" s="150"/>
+      <c r="U16" s="148"/>
+      <c r="V16" s="144"/>
+      <c r="W16" s="144"/>
+    </row>
+    <row r="17" spans="1:21" s="101" customFormat="1" ht="45.75">
+      <c r="A17" s="145">
+        <v>117633</v>
+      </c>
+      <c r="B17" s="154" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="121" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="146" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="118" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="148" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="149">
+        <v>0</v>
+      </c>
+      <c r="H17" s="149">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="I17" s="148" t="s">
+        <v>76</v>
+      </c>
+      <c r="J17" s="148"/>
+      <c r="K17" s="148"/>
+      <c r="L17" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="150"/>
+      <c r="N17" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="O17" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="150"/>
+      <c r="R17" s="150"/>
+      <c r="S17" s="148"/>
+      <c r="T17" s="150"/>
+      <c r="U17" s="148"/>
+    </row>
+    <row r="18" spans="1:21" s="101" customFormat="1" ht="91.5">
+      <c r="A18" s="153"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="152" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="148" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="149">
+        <v>0</v>
+      </c>
+      <c r="H18" s="149" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="164" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="150"/>
+      <c r="N18" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="O18" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="P18" s="150"/>
+      <c r="Q18" s="150"/>
+      <c r="R18" s="150"/>
+      <c r="S18" s="148"/>
+      <c r="T18" s="150"/>
+      <c r="U18" s="148"/>
+    </row>
+    <row r="19" spans="1:21" s="101" customFormat="1" ht="30.75">
+      <c r="A19" s="165"/>
+      <c r="B19" s="165"/>
+      <c r="C19" s="166"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="147" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="167" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="167">
+        <v>0</v>
+      </c>
+      <c r="H19" s="167">
+        <v>3</v>
+      </c>
+      <c r="I19" s="167" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="167"/>
+      <c r="K19" s="167"/>
+      <c r="L19" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="167"/>
+      <c r="N19" s="167" t="s">
+        <v>66</v>
+      </c>
+      <c r="O19" s="167" t="s">
+        <v>29</v>
+      </c>
+      <c r="P19" s="167"/>
+      <c r="Q19" s="167"/>
+      <c r="R19" s="167"/>
+      <c r="S19" s="167"/>
+      <c r="T19" s="167"/>
+      <c r="U19" s="167"/>
+    </row>
+    <row r="20" spans="1:21" s="101" customFormat="1" ht="45.75">
+      <c r="A20" s="165"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="166"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="147" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="167" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="167">
+        <v>0</v>
+      </c>
+      <c r="H20" s="167">
+        <v>1600</v>
+      </c>
+      <c r="I20" s="167" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="167"/>
+      <c r="K20" s="167"/>
+      <c r="L20" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" s="167"/>
+      <c r="N20" s="167" t="s">
+        <v>66</v>
+      </c>
+      <c r="O20" s="167" t="s">
+        <v>29</v>
+      </c>
+      <c r="P20" s="167"/>
+      <c r="Q20" s="167"/>
+      <c r="R20" s="167"/>
+      <c r="S20" s="167"/>
+      <c r="T20" s="167"/>
+      <c r="U20" s="167"/>
+    </row>
+    <row r="21" spans="1:21" s="101" customFormat="1" ht="60.75">
+      <c r="A21" s="165"/>
+      <c r="B21" s="165"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="147" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="167" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="167">
+        <v>0</v>
+      </c>
+      <c r="H21" s="167">
+        <v>46</v>
+      </c>
+      <c r="I21" s="167" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21" s="167"/>
+      <c r="K21" s="167"/>
+      <c r="L21" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="167"/>
+      <c r="N21" s="167" t="s">
+        <v>66</v>
+      </c>
+      <c r="O21" s="167" t="s">
+        <v>29</v>
+      </c>
+      <c r="P21" s="167"/>
+      <c r="Q21" s="167"/>
+      <c r="R21" s="167"/>
+      <c r="S21" s="167"/>
+      <c r="T21" s="167"/>
+      <c r="U21" s="167"/>
+    </row>
+    <row r="22" spans="1:21" s="101" customFormat="1" ht="91.5">
+      <c r="A22" s="165"/>
+      <c r="B22" s="165"/>
+      <c r="C22" s="166"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="147" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="167" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="167">
+        <v>0</v>
+      </c>
+      <c r="H22" s="167">
+        <v>6</v>
+      </c>
+      <c r="I22" s="167" t="s">
+        <v>85</v>
+      </c>
+      <c r="J22" s="167"/>
+      <c r="K22" s="167"/>
+      <c r="L22" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" s="167"/>
+      <c r="N22" s="167" t="s">
+        <v>66</v>
+      </c>
+      <c r="O22" s="167" t="s">
+        <v>29</v>
+      </c>
+      <c r="P22" s="167"/>
+      <c r="Q22" s="167" t="s">
+        <v>86</v>
+      </c>
+      <c r="R22" s="167" t="s">
+        <v>67</v>
+      </c>
+      <c r="S22" s="167"/>
+      <c r="T22" s="167"/>
+      <c r="U22" s="167"/>
+    </row>
+    <row r="23" spans="1:21" s="101" customFormat="1" ht="60.75">
+      <c r="A23" s="168">
+        <v>1000715</v>
+      </c>
+      <c r="B23" s="168" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="169" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="170">
+        <v>2994199</v>
+      </c>
+      <c r="E23" s="147"/>
+      <c r="F23" s="167" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="167">
+        <v>0</v>
+      </c>
+      <c r="H23" s="167" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" s="167" t="s">
+        <v>90</v>
+      </c>
+      <c r="J23" s="167"/>
+      <c r="K23" s="167"/>
+      <c r="L23" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="167"/>
+      <c r="N23" s="167"/>
+      <c r="O23" s="167"/>
+      <c r="P23" s="167"/>
+      <c r="Q23" s="167"/>
+      <c r="R23" s="167"/>
+      <c r="S23" s="167"/>
+      <c r="T23" s="167"/>
+      <c r="U23" s="167"/>
+    </row>
+    <row r="24" spans="1:21" s="101" customFormat="1" ht="45.75">
+      <c r="A24" s="165"/>
+      <c r="B24" s="165"/>
+      <c r="C24" s="166"/>
+      <c r="D24" s="165"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="167" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="167">
+        <v>0</v>
+      </c>
+      <c r="H24" s="167" t="s">
+        <v>89</v>
+      </c>
+      <c r="I24" s="167" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="167"/>
+      <c r="K24" s="167"/>
+      <c r="L24" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="167"/>
+      <c r="N24" s="167"/>
+      <c r="O24" s="167"/>
+      <c r="P24" s="167"/>
+      <c r="Q24" s="167"/>
+      <c r="R24" s="167"/>
+      <c r="S24" s="167"/>
+      <c r="T24" s="167"/>
+      <c r="U24" s="167"/>
+    </row>
+    <row r="25" spans="1:21" s="101" customFormat="1" ht="91.5">
+      <c r="A25" s="165"/>
+      <c r="B25" s="165"/>
+      <c r="C25" s="166"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="147" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="167" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="167">
+        <v>0</v>
+      </c>
+      <c r="H25" s="167">
+        <v>36</v>
+      </c>
+      <c r="I25" s="167" t="s">
+        <v>94</v>
+      </c>
+      <c r="J25" s="167"/>
+      <c r="K25" s="167"/>
+      <c r="L25" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="167"/>
+      <c r="N25" s="167"/>
+      <c r="O25" s="167"/>
+      <c r="P25" s="167"/>
+      <c r="Q25" s="167"/>
+      <c r="R25" s="167"/>
+      <c r="S25" s="167"/>
+      <c r="T25" s="167"/>
+      <c r="U25" s="167"/>
+    </row>
+    <row r="26" spans="1:21" s="101" customFormat="1" ht="45.75">
+      <c r="A26" s="165"/>
+      <c r="B26" s="165"/>
+      <c r="C26" s="166"/>
+      <c r="D26" s="165"/>
+      <c r="E26" s="147" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="167" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" s="167">
+        <v>0</v>
+      </c>
+      <c r="H26" s="167">
+        <v>8</v>
+      </c>
+      <c r="I26" s="167" t="s">
+        <v>97</v>
+      </c>
+      <c r="J26" s="167"/>
+      <c r="K26" s="167"/>
+      <c r="L26" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="167"/>
+      <c r="N26" s="167"/>
+      <c r="O26" s="167"/>
+      <c r="P26" s="167"/>
+      <c r="Q26" s="167"/>
+      <c r="R26" s="167"/>
+      <c r="S26" s="167"/>
+      <c r="T26" s="167"/>
+      <c r="U26" s="167"/>
+    </row>
+    <row r="27" spans="1:21" s="101" customFormat="1" ht="60.75">
+      <c r="A27" s="165"/>
+      <c r="B27" s="165"/>
+      <c r="C27" s="166"/>
+      <c r="D27" s="165"/>
+      <c r="E27" s="147" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="167" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" s="167">
+        <v>0</v>
+      </c>
+      <c r="H27" s="167">
+        <v>10100</v>
+      </c>
+      <c r="I27" s="167" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27" s="167"/>
+      <c r="K27" s="167"/>
+      <c r="L27" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" s="167"/>
+      <c r="N27" s="167"/>
+      <c r="O27" s="167"/>
+      <c r="P27" s="167"/>
+      <c r="Q27" s="167"/>
+      <c r="R27" s="167"/>
+      <c r="S27" s="167"/>
+      <c r="T27" s="167"/>
+      <c r="U27" s="167"/>
+    </row>
+    <row r="28" spans="1:21" s="101" customFormat="1" ht="45.75">
+      <c r="A28" s="165"/>
+      <c r="B28" s="165"/>
+      <c r="C28" s="166"/>
+      <c r="D28" s="165"/>
+      <c r="E28" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="167" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="167">
+        <v>0</v>
+      </c>
+      <c r="H28" s="167">
+        <v>5</v>
+      </c>
+      <c r="I28" s="167" t="s">
+        <v>101</v>
+      </c>
+      <c r="J28" s="167"/>
+      <c r="K28" s="167"/>
+      <c r="L28" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="167"/>
+      <c r="N28" s="167"/>
+      <c r="O28" s="167"/>
+      <c r="P28" s="167"/>
+      <c r="Q28" s="167"/>
+      <c r="R28" s="167"/>
+      <c r="S28" s="167"/>
+      <c r="T28" s="167"/>
+      <c r="U28" s="167"/>
+    </row>
+    <row r="29" spans="1:21" s="101" customFormat="1" ht="76.5">
+      <c r="A29" s="171"/>
+      <c r="B29" s="171"/>
+      <c r="C29" s="172"/>
+      <c r="D29" s="171"/>
+      <c r="E29" s="147" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="167" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="167">
+        <v>0</v>
+      </c>
+      <c r="H29" s="167">
+        <v>4</v>
+      </c>
+      <c r="I29" s="167" t="s">
+        <v>102</v>
+      </c>
+      <c r="J29" s="167"/>
+      <c r="K29" s="167"/>
+      <c r="L29" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" s="167"/>
+      <c r="N29" s="167"/>
+      <c r="O29" s="167"/>
+      <c r="P29" s="167"/>
+      <c r="Q29" s="167"/>
+      <c r="R29" s="167"/>
+      <c r="S29" s="167"/>
+      <c r="T29" s="167"/>
+      <c r="U29" s="167"/>
+    </row>
+  </sheetData>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S18" xr:uid="{CBB3BE96-769B-444E-8F19-B98B8A733B77}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R18" xr:uid="{3E5BD2C4-7544-4588-A369-02B6A7760BF9}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L29" xr:uid="{93D95E4A-2418-4F02-BE48-19085DA84CFB}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T18" xr:uid="{C2D3F982-E068-4D51-9E16-80E76097186A}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M18" xr:uid="{65F63630-8818-4CFE-840F-9981A10EF94A}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O18" xr:uid="{4A8BEEC2-2B38-4CA7-B2B1-346B4B79E8CD}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N18" xr:uid="{2487365A-4460-4174-9145-DF094CCDCA1B}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P18" xr:uid="{EE07AFA3-F39E-4B10-8B47-6CB08A2C6EC9}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q18" xr:uid="{35F880E9-AE57-4F56-B3A8-3063679FE002}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{B017DF94-98BD-4F20-B777-E60AB2916023}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A6BA0BDA-3315-4E35-8DBE-26FCCAFECD30}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E18</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874F726E-0702-4819-A4CE-990D59EFF568}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
@@ -1470,7 +3472,7 @@
     <col min="3" max="3" width="18.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.140625" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" customWidth="1"/>
-    <col min="6" max="6" width="29.140625" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
@@ -1485,79 +3487,80 @@
     <col min="19" max="19" width="20.7109375" customWidth="1"/>
     <col min="20" max="20" width="30" customWidth="1"/>
     <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="82.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="30.75">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="67" t="s">
+    <row r="1" spans="1:23" ht="30.75">
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="68" t="s">
+      <c r="J1" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="68" t="s">
+      <c r="K1" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="73" t="s">
+      <c r="L1" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="74" t="s">
+      <c r="M1" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="73" t="s">
+      <c r="N1" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="73" t="s">
+      <c r="O1" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="74" t="s">
+      <c r="P1" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="74" t="s">
+      <c r="Q1" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="75" t="s">
+      <c r="R1" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="76" t="s">
+      <c r="S1" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="75" t="s">
+      <c r="T1" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="76" t="s">
+      <c r="U1" s="73" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="45.75" customHeight="1">
+    <row r="2" spans="1:23" ht="45.75" customHeight="1">
       <c r="A2" s="43">
         <v>130633</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="C2" s="45" t="s">
         <v>22</v>
@@ -1578,37 +3581,37 @@
         <v>50</v>
       </c>
       <c r="I2" s="38" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="J2" s="47" t="s">
         <v>26</v>
       </c>
       <c r="K2" s="47"/>
-      <c r="L2" s="77" t="s">
+      <c r="L2" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="70"/>
-      <c r="N2" s="78" t="s">
+      <c r="M2" s="67"/>
+      <c r="N2" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="70"/>
-      <c r="U2" s="79"/>
-    </row>
-    <row r="3" spans="1:21" ht="121.5">
-      <c r="A3" s="48"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="76"/>
+    </row>
+    <row r="3" spans="1:23" ht="366">
+      <c r="A3" s="98"/>
       <c r="B3" s="49"/>
       <c r="C3" s="50"/>
       <c r="D3" s="51"/>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -1617,28 +3620,28 @@
         <v>350</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="J3" s="47" t="s">
         <v>26</v>
       </c>
       <c r="K3" s="52"/>
-      <c r="L3" s="77" t="s">
+      <c r="L3" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="70"/>
-      <c r="N3" s="78" t="s">
+      <c r="M3" s="67"/>
+      <c r="N3" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="70"/>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="70"/>
-      <c r="U3" s="79"/>
-    </row>
-    <row r="4" spans="1:21" ht="259.5">
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="76"/>
+    </row>
+    <row r="4" spans="1:23" ht="259.5">
       <c r="A4" s="53"/>
       <c r="B4" s="54"/>
       <c r="C4" s="55"/>
@@ -1647,7 +3650,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
@@ -1656,41 +3659,41 @@
         <v>3</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="J4" s="47" t="s">
         <v>26</v>
       </c>
       <c r="K4" s="57"/>
-      <c r="L4" s="77" t="s">
+      <c r="L4" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="70"/>
-      <c r="N4" s="78" t="s">
+      <c r="M4" s="67"/>
+      <c r="N4" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="P4" s="70"/>
-      <c r="Q4" s="70" t="s">
-        <v>35</v>
-      </c>
-      <c r="R4" s="70" t="s">
-        <v>36</v>
-      </c>
-      <c r="S4" s="79"/>
-      <c r="T4" s="70" t="s">
-        <v>37</v>
-      </c>
-      <c r="U4" s="79"/>
-    </row>
-    <row r="5" spans="1:21" ht="90.75" customHeight="1">
+      <c r="O4" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="R4" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="S4" s="76"/>
+      <c r="T4" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="U4" s="76"/>
+    </row>
+    <row r="5" spans="1:23" ht="90.75" customHeight="1">
       <c r="A5" s="47">
         <v>1061012</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="C5" s="47"/>
       <c r="D5" s="46">
@@ -1706,29 +3709,29 @@
         <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="77" t="s">
+      <c r="L5" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="70"/>
-      <c r="N5" s="78" t="s">
+      <c r="M5" s="67"/>
+      <c r="N5" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="70"/>
-      <c r="P5" s="70"/>
-      <c r="Q5" s="70"/>
-      <c r="R5" s="70"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="70"/>
-      <c r="U5" s="79"/>
-    </row>
-    <row r="6" spans="1:21" ht="70.5" customHeight="1">
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="76"/>
+    </row>
+    <row r="6" spans="1:23" ht="70.5" customHeight="1">
       <c r="A6" s="52"/>
       <c r="B6" s="49"/>
       <c r="C6" s="52"/>
@@ -1743,144 +3746,144 @@
         <v>0</v>
       </c>
       <c r="H6" s="5">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="77" t="s">
+      <c r="L6" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="70"/>
-      <c r="N6" s="78" t="s">
+      <c r="M6" s="67"/>
+      <c r="N6" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="79" t="s">
-        <v>43</v>
-      </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="79"/>
-    </row>
-    <row r="7" spans="1:21" ht="45.75">
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="76" t="s">
+        <v>111</v>
+      </c>
+      <c r="T6" s="67"/>
+      <c r="U6" s="76"/>
+    </row>
+    <row r="7" spans="1:23" ht="45.75">
       <c r="A7" s="52"/>
       <c r="B7" s="49"/>
       <c r="C7" s="52"/>
       <c r="D7" s="58"/>
       <c r="E7" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="39">
-        <v>570</v>
+      <c r="H7" s="39" t="s">
+        <v>112</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="77" t="s">
+      <c r="L7" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="70"/>
-      <c r="N7" s="78" t="s">
+      <c r="M7" s="67"/>
+      <c r="N7" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="70"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="79" t="s">
-        <v>43</v>
-      </c>
-      <c r="T7" s="70"/>
-      <c r="U7" s="79"/>
-    </row>
-    <row r="8" spans="1:21" ht="45.75">
+      <c r="O7" s="67"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="76" t="s">
+        <v>111</v>
+      </c>
+      <c r="T7" s="67"/>
+      <c r="U7" s="76"/>
+    </row>
+    <row r="8" spans="1:23" ht="45.75">
       <c r="A8" s="52"/>
       <c r="B8" s="49"/>
       <c r="C8" s="52"/>
       <c r="D8" s="58"/>
       <c r="E8" s="23" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
       </c>
       <c r="H8" s="5">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="77" t="s">
+      <c r="L8" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M8" s="70"/>
-      <c r="N8" s="78" t="s">
+      <c r="M8" s="67"/>
+      <c r="N8" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="70"/>
-      <c r="P8" s="70"/>
-      <c r="Q8" s="70"/>
-      <c r="R8" s="70"/>
-      <c r="S8" s="79"/>
-      <c r="T8" s="70"/>
-      <c r="U8" s="79"/>
-    </row>
-    <row r="9" spans="1:21" ht="50.25">
+      <c r="O8" s="67"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="76"/>
+      <c r="T8" s="67"/>
+      <c r="U8" s="76"/>
+    </row>
+    <row r="9" spans="1:23" ht="45.75">
       <c r="A9" s="52"/>
       <c r="B9" s="49"/>
       <c r="C9" s="52"/>
       <c r="D9" s="58"/>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="77" t="s">
+      <c r="L9" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M9" s="70"/>
-      <c r="N9" s="78" t="s">
+      <c r="M9" s="67"/>
+      <c r="N9" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O9" s="70"/>
-      <c r="P9" s="70"/>
-      <c r="Q9" s="70"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="79"/>
-      <c r="T9" s="70"/>
-      <c r="U9" s="79"/>
-    </row>
-    <row r="10" spans="1:21" ht="45.75">
+      <c r="O9" s="67"/>
+      <c r="P9" s="67"/>
+      <c r="Q9" s="67"/>
+      <c r="R9" s="67"/>
+      <c r="S9" s="76"/>
+      <c r="T9" s="67"/>
+      <c r="U9" s="76"/>
+    </row>
+    <row r="10" spans="1:23" ht="45.75">
       <c r="A10" s="57"/>
       <c r="B10" s="54"/>
       <c r="C10" s="57"/>
@@ -1890,52 +3893,52 @@
         <v>Medium Enterprises</v>
       </c>
       <c r="F10" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="77" t="s">
+      <c r="L10" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="70"/>
-      <c r="N10" s="78" t="s">
+      <c r="M10" s="67"/>
+      <c r="N10" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="70"/>
-      <c r="P10" s="70"/>
-      <c r="Q10" s="70"/>
-      <c r="R10" s="70"/>
-      <c r="S10" s="79"/>
-      <c r="T10" s="70"/>
-      <c r="U10" s="79"/>
-    </row>
-    <row r="11" spans="1:21" s="1" customFormat="1" ht="161.25" customHeight="1">
+      <c r="O10" s="67"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="76"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="76"/>
+    </row>
+    <row r="11" spans="1:23" s="1" customFormat="1" ht="161.25" customHeight="1">
       <c r="A11" s="60">
         <v>134019</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="D11" s="46">
         <v>3000000</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -1944,71 +3947,76 @@
         <v>70</v>
       </c>
       <c r="I11" s="61" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
-      <c r="L11" s="77" t="s">
+      <c r="L11" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M11" s="70"/>
-      <c r="N11" s="78" t="s">
+      <c r="M11" s="67"/>
+      <c r="N11" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O11" s="70"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="70"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="79"/>
-      <c r="T11" s="70"/>
-      <c r="U11" s="79"/>
-    </row>
-    <row r="12" spans="1:21" s="2" customFormat="1" ht="91.5">
-      <c r="A12" s="62"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="23" t="s">
-        <v>52</v>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="76"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="76"/>
+    </row>
+    <row r="12" spans="1:23" s="2" customFormat="1" ht="91.5">
+      <c r="A12" s="79"/>
+      <c r="B12" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="80" t="s">
+        <v>58</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G12" s="5">
         <v>0</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="81">
         <v>20</v>
       </c>
-      <c r="I12" s="63"/>
-      <c r="J12" s="35"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="75"/>
       <c r="K12" s="35"/>
-      <c r="L12" s="77" t="s">
+      <c r="L12" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M12" s="70"/>
-      <c r="N12" s="78" t="s">
+      <c r="M12" s="67"/>
+      <c r="N12" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="70"/>
-      <c r="P12" s="70"/>
-      <c r="Q12" s="70"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="79"/>
-      <c r="T12" s="70"/>
-      <c r="U12" s="79"/>
-    </row>
-    <row r="13" spans="1:21" ht="183" customHeight="1">
+      <c r="O12" s="67"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="76"/>
+      <c r="T12" s="67"/>
+      <c r="U12" s="76"/>
+      <c r="W12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="183" customHeight="1">
       <c r="A13" s="43">
         <v>117633</v>
       </c>
-      <c r="B13" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="46">
+      <c r="B13" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="51">
         <v>2201100</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -2023,38 +4031,38 @@
       <c r="H13" s="32">
         <v>0.05</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>58</v>
+      <c r="I13" s="82" t="s">
+        <v>117</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="77" t="s">
+      <c r="L13" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M13" s="70"/>
-      <c r="N13" s="78" t="s">
+      <c r="M13" s="67"/>
+      <c r="N13" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O13" s="70"/>
-      <c r="P13" s="70"/>
-      <c r="Q13" s="70"/>
-      <c r="R13" s="70"/>
-      <c r="S13" s="79" t="s">
-        <v>59</v>
-      </c>
-      <c r="T13" s="70"/>
-      <c r="U13" s="79"/>
-    </row>
-    <row r="14" spans="1:21" ht="168" customHeight="1">
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="76" t="s">
+        <v>118</v>
+      </c>
+      <c r="T13" s="67"/>
+      <c r="U13" s="76"/>
+    </row>
+    <row r="14" spans="1:23" ht="168" customHeight="1">
       <c r="A14" s="48"/>
       <c r="B14" s="52"/>
-      <c r="C14" s="65"/>
+      <c r="C14" s="62"/>
       <c r="D14" s="51"/>
       <c r="E14" s="3" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G14" s="5">
         <v>0</v>
@@ -2063,35 +4071,35 @@
         <v>1300</v>
       </c>
       <c r="I14" s="42" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="77" t="s">
+      <c r="L14" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M14" s="70"/>
-      <c r="N14" s="78" t="s">
+      <c r="M14" s="67"/>
+      <c r="N14" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O14" s="70"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="70"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="79"/>
-      <c r="T14" s="70"/>
-      <c r="U14" s="79"/>
-    </row>
-    <row r="15" spans="1:21" ht="45.75">
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="76"/>
+      <c r="T14" s="67"/>
+      <c r="U14" s="76"/>
+    </row>
+    <row r="15" spans="1:23" ht="45.75">
       <c r="A15" s="48"/>
       <c r="B15" s="52"/>
-      <c r="C15" s="65"/>
+      <c r="C15" s="62"/>
       <c r="D15" s="51"/>
       <c r="E15" s="23" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="G15" s="5">
         <v>0</v>
@@ -2100,35 +4108,35 @@
         <v>3</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="77" t="s">
+      <c r="L15" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M15" s="70"/>
-      <c r="N15" s="78" t="s">
+      <c r="M15" s="67"/>
+      <c r="N15" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O15" s="70"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="70"/>
-      <c r="S15" s="79"/>
-      <c r="T15" s="70"/>
-      <c r="U15" s="79"/>
-    </row>
-    <row r="16" spans="1:21" ht="76.5">
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="76"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="76"/>
+    </row>
+    <row r="16" spans="1:23" ht="76.5">
       <c r="A16" s="48"/>
       <c r="B16" s="52"/>
-      <c r="C16" s="65"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="51"/>
       <c r="E16" s="3" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G16" s="5">
         <v>0</v>
@@ -2137,35 +4145,35 @@
         <v>1600</v>
       </c>
       <c r="I16" s="42" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="77" t="s">
+      <c r="L16" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M16" s="70"/>
-      <c r="N16" s="78" t="s">
+      <c r="M16" s="67"/>
+      <c r="N16" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O16" s="70"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="70"/>
-      <c r="R16" s="70"/>
-      <c r="S16" s="79"/>
-      <c r="T16" s="70"/>
-      <c r="U16" s="79"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="76"/>
+      <c r="T16" s="67"/>
+      <c r="U16" s="76"/>
     </row>
     <row r="17" spans="1:21" ht="76.5">
       <c r="A17" s="48"/>
       <c r="B17" s="52"/>
-      <c r="C17" s="65"/>
+      <c r="C17" s="62"/>
       <c r="D17" s="51"/>
       <c r="E17" s="23" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G17" s="5">
         <v>0</v>
@@ -2174,29 +4182,29 @@
         <v>46</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="77" t="s">
+      <c r="L17" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="70"/>
-      <c r="N17" s="78" t="s">
+      <c r="M17" s="67"/>
+      <c r="N17" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70"/>
-      <c r="R17" s="70"/>
-      <c r="S17" s="79"/>
-      <c r="T17" s="70"/>
-      <c r="U17" s="79"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="76"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="76"/>
     </row>
     <row r="18" spans="1:21" ht="121.5">
       <c r="A18" s="53"/>
       <c r="B18" s="57"/>
-      <c r="C18" s="66"/>
+      <c r="C18" s="63"/>
       <c r="D18" s="56"/>
       <c r="E18" s="3" t="s">
         <v>19</v>
@@ -2211,32 +4219,32 @@
         <v>6</v>
       </c>
       <c r="I18" s="42" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="77" t="s">
+      <c r="K18" s="66"/>
+      <c r="L18" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M18" s="70"/>
-      <c r="N18" s="78" t="s">
+      <c r="M18" s="67"/>
+      <c r="N18" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O18" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="70" t="s">
-        <v>35</v>
-      </c>
-      <c r="R18" s="70" t="s">
-        <v>36</v>
-      </c>
-      <c r="S18" s="79"/>
-      <c r="T18" s="70" t="s">
-        <v>37</v>
-      </c>
-      <c r="U18" s="79"/>
+      <c r="O18" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="R18" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="S18" s="76"/>
+      <c r="T18" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="U18" s="76"/>
     </row>
   </sheetData>
   <dataValidations count="9">
@@ -2270,7 +4278,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C13" r:id="rId1" xr:uid="{CE5DD5C7-7986-4F7B-AD7C-255694C6DAC7}"/>
-    <hyperlink ref="C2:C4" r:id="rId2" display="https://www.undp.org/vietnam/projects/catalysing-sustainable-shift-towards-e-mobility" xr:uid="{D2709AFB-4C66-4C21-B9E8-9BD577A0D9F3}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{AC6099BE-5B14-4B8B-A8EA-DF2DE59FB182}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -2289,14 +4297,960 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6C49273-312D-42BB-A533-C1ED9908BEC3}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="31.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="9" max="9" width="68.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="13" max="13" width="32.5703125" customWidth="1"/>
+    <col min="15" max="15" width="35" customWidth="1"/>
+    <col min="16" max="16" width="22.5703125" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="O1" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="45.75">
+      <c r="A2" s="138" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="135" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="139" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="129">
+        <v>896583</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="32">
+        <v>50</v>
+      </c>
+      <c r="I2" s="89" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="122" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="17"/>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="121.5">
+      <c r="A3" s="138"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="32">
+        <v>350</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="17"/>
+    </row>
+    <row r="4" spans="1:19" ht="336">
+      <c r="A4" s="138"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="32">
+        <v>3</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="O4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="52.5" customHeight="1">
+      <c r="A5" s="126">
+        <v>1061012</v>
+      </c>
+      <c r="B5" s="135" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="136"/>
+      <c r="D5" s="137">
+        <v>1128978</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>45</v>
+      </c>
+      <c r="I5" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="O5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="70.5" customHeight="1">
+      <c r="A6" s="126"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="O6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="45.75">
+      <c r="A7" s="126"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="27">
+        <v>570</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="O7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="60.75">
+      <c r="A8" s="126"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>70</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+    </row>
+    <row r="9" spans="1:19" ht="76.5">
+      <c r="A9" s="126"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>370</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+    </row>
+    <row r="10" spans="1:19" ht="110.25" customHeight="1">
+      <c r="A10" s="126"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+    </row>
+    <row r="11" spans="1:19" ht="37.5" customHeight="1">
+      <c r="A11" s="126"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="136"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="23" t="str">
+        <f>'Beneficiary Categories'!A15</f>
+        <v>Medium Enterprises</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>4</v>
+      </c>
+      <c r="I11" s="97" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="O11" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" s="1" customFormat="1" ht="88.5" customHeight="1">
+      <c r="A12" s="130">
+        <v>134019</v>
+      </c>
+      <c r="B12" s="131" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="127" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="96">
+        <v>33000</v>
+      </c>
+      <c r="I12" s="133" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="O12" t="s">
+        <v>66</v>
+      </c>
+      <c r="P12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q12"/>
+      <c r="R12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" s="1" customFormat="1" ht="143.25" customHeight="1">
+      <c r="A13" s="130"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>70</v>
+      </c>
+      <c r="I13" s="133"/>
+      <c r="J13" s="123"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="123"/>
+      <c r="M13" s="7"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+    </row>
+    <row r="14" spans="1:19" s="1" customFormat="1" ht="105.75" customHeight="1">
+      <c r="A14" s="130"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="91" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="92">
+        <v>0</v>
+      </c>
+      <c r="H14" s="92">
+        <v>150</v>
+      </c>
+      <c r="I14" s="133"/>
+      <c r="J14" s="123"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="123"/>
+      <c r="M14" s="7"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+    </row>
+    <row r="15" spans="1:19" s="1" customFormat="1" ht="105" customHeight="1">
+      <c r="A15" s="130"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="93" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="94" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="95">
+        <v>0</v>
+      </c>
+      <c r="H15" s="95">
+        <v>8</v>
+      </c>
+      <c r="I15" s="134"/>
+      <c r="J15" s="123"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="123"/>
+      <c r="M15" s="7"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+    </row>
+    <row r="16" spans="1:19" s="2" customFormat="1" ht="76.5">
+      <c r="A16" s="130"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="93" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="94" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="95">
+        <v>0</v>
+      </c>
+      <c r="H16" s="95">
+        <v>2</v>
+      </c>
+      <c r="I16" s="133"/>
+      <c r="J16" s="124"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="124"/>
+      <c r="M16" s="30"/>
+      <c r="O16" t="s">
+        <v>66</v>
+      </c>
+      <c r="P16" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q16"/>
+      <c r="R16" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="122.25" customHeight="1">
+      <c r="A17" s="125">
+        <v>117633</v>
+      </c>
+      <c r="B17" s="127" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="128" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="129">
+        <v>2201100</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="I17" s="83" t="s">
+        <v>131</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="O17" t="s">
+        <v>66</v>
+      </c>
+      <c r="P17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="168" customHeight="1">
+      <c r="A18" s="126"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="87" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="84" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="O18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="30.75">
+      <c r="A19" s="126"/>
+      <c r="B19" s="127"/>
+      <c r="C19" s="128"/>
+      <c r="D19" s="129"/>
+      <c r="E19" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="88">
+        <v>3</v>
+      </c>
+      <c r="I19" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="123"/>
+      <c r="M19" s="17"/>
+      <c r="O19" t="s">
+        <v>66</v>
+      </c>
+      <c r="P19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="76.5">
+      <c r="A20" s="126"/>
+      <c r="B20" s="127"/>
+      <c r="C20" s="128"/>
+      <c r="D20" s="129"/>
+      <c r="E20" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="88">
+        <v>1600</v>
+      </c>
+      <c r="I20" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="17"/>
+      <c r="O20" t="s">
+        <v>66</v>
+      </c>
+      <c r="P20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="76.5">
+      <c r="A21" s="126"/>
+      <c r="B21" s="127"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="88">
+        <v>46</v>
+      </c>
+      <c r="I21" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="123"/>
+      <c r="M21" s="17"/>
+      <c r="O21" t="s">
+        <v>66</v>
+      </c>
+      <c r="P21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="137.25">
+      <c r="A22" s="126"/>
+      <c r="B22" s="127"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="88">
+        <v>6</v>
+      </c>
+      <c r="I22" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="124"/>
+      <c r="M22" s="17"/>
+      <c r="O22" t="s">
+        <v>66</v>
+      </c>
+      <c r="P22" t="s">
+        <v>29</v>
+      </c>
+      <c r="R22" t="s">
+        <v>86</v>
+      </c>
+      <c r="S22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="44.25" customHeight="1">
+      <c r="A23" s="125" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="127" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="128"/>
+      <c r="D23" s="140">
+        <v>2994199</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="87"/>
+      <c r="I23" s="83" t="s">
+        <v>135</v>
+      </c>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" spans="1:19" ht="52.5" customHeight="1">
+      <c r="A24" s="126"/>
+      <c r="B24" s="127"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="87"/>
+      <c r="I24" s="84" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="123"/>
+      <c r="M24" s="37"/>
+    </row>
+    <row r="25" spans="1:19" ht="76.5">
+      <c r="A25" s="126"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="129"/>
+      <c r="E25" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="88"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="123"/>
+      <c r="M25" s="17"/>
+    </row>
+    <row r="26" spans="1:19" ht="40.5" customHeight="1">
+      <c r="A26" s="126"/>
+      <c r="B26" s="127"/>
+      <c r="C26" s="128"/>
+      <c r="D26" s="129"/>
+      <c r="E26" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="88"/>
+      <c r="I26" s="86" t="s">
+        <v>136</v>
+      </c>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="123"/>
+      <c r="M26" s="17"/>
+    </row>
+    <row r="27" spans="1:19" ht="37.5">
+      <c r="A27" s="126"/>
+      <c r="B27" s="127"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="129"/>
+      <c r="E27" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="88"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="124"/>
+      <c r="M27" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="D23:D27"/>
+    <mergeCell ref="L23:L27"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A5:A11"/>
+    <mergeCell ref="B5:B11"/>
+    <mergeCell ref="C5:C11"/>
+    <mergeCell ref="D5:D11"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L12:L16"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="L17:L22"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="I12:I16"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S22" xr:uid="{0F718CCA-00B4-42C1-84D0-4A1FEABF9813}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R22" xr:uid="{01B0D87C-39E9-424A-B243-6769EF208A26}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q22" xr:uid="{F9C284A2-18CC-42C1-A802-593F5762F0DE}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P27" xr:uid="{57053484-5A37-42A2-ADC4-555165F10156}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O27" xr:uid="{055BA81B-9EF7-4EA5-AA1F-10A8E3A3E3A0}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C17" r:id="rId1" xr:uid="{286A0975-6C52-4D4D-9BAA-AF594639A6CE}"/>
+    <hyperlink ref="C2:C4" r:id="rId2" display="https://www.undp.org/vietnam/projects/catalysing-sustainable-shift-towards-e-mobility" xr:uid="{3A0FE6BB-856F-4F5C-9C8A-11D425A850A8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1A37DB-72C0-4C16-80D3-04ED5F162378}">
   <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="32.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.140625" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" customWidth="1"/>
     <col min="6" max="6" width="29.140625" customWidth="1"/>
@@ -2346,10 +5300,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>13</v>
@@ -2368,16 +5322,16 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="45.75">
-      <c r="A2" s="91" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="92" t="s">
+      <c r="A2" s="138" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="83">
+      <c r="D2" s="129">
         <v>896583</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -2393,13 +5347,13 @@
         <v>50</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="85" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85" t="s">
+      <c r="K2" s="122"/>
+      <c r="L2" s="122" t="s">
         <v>27</v>
       </c>
       <c r="M2" s="17"/>
@@ -2407,19 +5361,19 @@
         <v>28</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="121.5">
-      <c r="A3" s="91"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="83"/>
+      <c r="A3" s="138"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="129"/>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -2428,23 +5382,23 @@
         <v>350</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
+        <v>137</v>
+      </c>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
       <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:19" ht="259.5">
-      <c r="A4" s="91"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="83"/>
+      <c r="A4" s="138"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="129"/>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -2453,36 +5407,36 @@
         <v>3</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
+        <v>107</v>
+      </c>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
       <c r="M4" s="36" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="R4" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S4" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="45.75" customHeight="1">
-      <c r="A5" s="82">
+      <c r="A5" s="126">
         <v>1061012</v>
       </c>
-      <c r="B5" s="92" t="s">
+      <c r="B5" s="135" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="94"/>
-      <c r="D5" s="95">
+      <c r="C5" s="136"/>
+      <c r="D5" s="137">
         <v>1128978</v>
       </c>
       <c r="E5" s="23" t="s">
@@ -2498,7 +5452,7 @@
         <v>45</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
@@ -2508,14 +5462,14 @@
         <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="70.5" customHeight="1">
-      <c r="A6" s="82"/>
-      <c r="B6" s="92"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="95"/>
+      <c r="A6" s="126"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
       <c r="E6" s="23" t="s">
         <v>41</v>
       </c>
@@ -2529,29 +5483,29 @@
         <v>4.2</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="O6" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="P6" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="45.75">
-      <c r="A7" s="82"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="95"/>
+      <c r="A7" s="126"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
       <c r="E7" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" s="9">
         <v>0</v>
@@ -2560,7 +5514,7 @@
         <v>570</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
@@ -2570,19 +5524,19 @@
         <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="30.75">
-      <c r="A8" s="82"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
+      <c r="A8" s="126"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
       <c r="E8" s="23" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
@@ -2591,7 +5545,7 @@
         <v>70</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -2599,15 +5553,15 @@
       <c r="M8" s="17"/>
     </row>
     <row r="9" spans="1:19" ht="50.25">
-      <c r="A9" s="82"/>
-      <c r="B9" s="92"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="95"/>
+      <c r="A9" s="126"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
       <c r="E9" s="3" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -2616,7 +5570,7 @@
         <v>370</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -2624,16 +5578,16 @@
       <c r="M9" s="17"/>
     </row>
     <row r="10" spans="1:19" ht="37.5">
-      <c r="A10" s="82"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="95"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="137"/>
       <c r="E10" s="23" t="str">
         <f>'Beneficiary Categories'!A15</f>
         <v>Medium Enterprises</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G10" s="9">
         <v>0</v>
@@ -2642,7 +5596,7 @@
         <v>4</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
@@ -2652,33 +5606,33 @@
         <v>28</v>
       </c>
       <c r="P10" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="R10" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S10" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:19" s="1" customFormat="1" ht="161.25" customHeight="1">
-      <c r="A11" s="80">
+      <c r="A11" s="130">
         <v>134019</v>
       </c>
-      <c r="B11" s="81" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="82" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="83">
+      <c r="B11" s="131" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="126" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="129">
         <v>3000000</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -2686,37 +5640,37 @@
       <c r="H11" s="4">
         <v>70</v>
       </c>
-      <c r="I11" s="84" t="s">
-        <v>54</v>
+      <c r="I11" s="133" t="s">
+        <v>115</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="O11" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P11" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="Q11"/>
       <c r="R11" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S11" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:19" s="2" customFormat="1" ht="91.5">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="83"/>
+      <c r="A12" s="130"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="129"/>
       <c r="E12" s="6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G12" s="16">
         <v>0</v>
@@ -2724,36 +5678,36 @@
       <c r="H12" s="16">
         <v>20</v>
       </c>
-      <c r="I12" s="84"/>
+      <c r="I12" s="133"/>
       <c r="J12" s="30"/>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
       <c r="O12" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="Q12"/>
       <c r="R12" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S12" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="183" customHeight="1">
-      <c r="A13" s="88">
+      <c r="A13" s="125">
         <v>117633</v>
       </c>
-      <c r="B13" s="89" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="90" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="83">
+      <c r="B13" s="127" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="128" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="129">
         <v>2201100</v>
       </c>
       <c r="E13" s="17" t="s">
@@ -2766,36 +5720,36 @@
         <v>0</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
-      <c r="L13" s="85" t="s">
+      <c r="L13" s="122" t="s">
         <v>27</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="O13" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P13" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="168" customHeight="1">
-      <c r="A14" s="82"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="83"/>
+      <c r="A14" s="126"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="129"/>
       <c r="E14" s="17" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G14" s="9">
         <v>0</v>
@@ -2804,31 +5758,31 @@
         <v>1300</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="86"/>
+      <c r="L14" s="123"/>
       <c r="M14" s="37" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="O14" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P14" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="30.75">
-      <c r="A15" s="82"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="83"/>
+      <c r="A15" s="126"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="128"/>
+      <c r="D15" s="129"/>
       <c r="E15" s="31" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="G15" s="9">
         <v>0</v>
@@ -2837,29 +5791,29 @@
         <v>3</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
-      <c r="L15" s="86"/>
+      <c r="L15" s="123"/>
       <c r="M15" s="17"/>
       <c r="O15" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P15" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="76.5">
-      <c r="A16" s="82"/>
-      <c r="B16" s="89"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="83"/>
+      <c r="A16" s="126"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="129"/>
       <c r="E16" s="17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G16" s="9">
         <v>0</v>
@@ -2868,29 +5822,29 @@
         <v>1600</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
-      <c r="L16" s="86"/>
+      <c r="L16" s="123"/>
       <c r="M16" s="17"/>
       <c r="O16" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P16" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="76.5">
-      <c r="A17" s="82"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="83"/>
+      <c r="A17" s="126"/>
+      <c r="B17" s="127"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="129"/>
       <c r="E17" s="31" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G17" s="9">
         <v>0</v>
@@ -2899,26 +5853,26 @@
         <v>46</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
-      <c r="L17" s="86"/>
+      <c r="L17" s="123"/>
       <c r="M17" s="17"/>
       <c r="O17" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P17" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="121.5">
-      <c r="A18" s="82"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="83"/>
+      <c r="A18" s="126"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="129"/>
       <c r="E18" s="17" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
@@ -2930,23 +5884,23 @@
         <v>6</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="87"/>
+      <c r="L18" s="124"/>
       <c r="M18" s="17"/>
       <c r="O18" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P18" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="R18" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="S18" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2999,7 +5953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3048,66 +6002,66 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="45.75">
-      <c r="A2" s="91" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="92" t="s">
+      <c r="A2" s="138" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="83">
+      <c r="D2" s="129">
         <v>896583</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="G2" s="4">
         <v>0</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="121.5">
-      <c r="A3" s="91"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="83"/>
+      <c r="A3" s="138"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="129"/>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="60.75">
-      <c r="A4" s="91"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="83"/>
+      <c r="A4" s="138"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="129"/>
       <c r="E4" s="3" t="str">
         <f>E2</f>
         <v xml:space="preserve">Policy or Regulatory Framework and pilot activities </v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -3120,39 +6074,39 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="45.75" customHeight="1">
-      <c r="A5" s="82">
+      <c r="A5" s="142">
         <v>1061012</v>
       </c>
-      <c r="B5" s="92" t="s">
+      <c r="B5" s="135" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="94"/>
-      <c r="D5" s="95">
+      <c r="C5" s="136"/>
+      <c r="D5" s="137">
         <v>1128978</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="G5" s="9">
         <v>0</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="70.5" customHeight="1">
-      <c r="A6" s="82"/>
-      <c r="B6" s="92"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="95"/>
+      <c r="A6" s="142"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
       <c r="E6" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>42</v>
@@ -3161,43 +6115,43 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45.75">
-      <c r="A7" s="82"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="95"/>
+      <c r="A7" s="142"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
       <c r="E7" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" s="9">
         <v>0</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30.75">
-      <c r="A8" s="82"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
+      <c r="A8" s="142"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
       <c r="E8" s="23" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
@@ -3206,19 +6160,19 @@
         <v>70</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="50.25">
-      <c r="A9" s="82"/>
-      <c r="B9" s="92"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="95"/>
+      <c r="A9" s="142"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
       <c r="E9" s="3" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -3227,20 +6181,20 @@
         <v>370</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="37.5">
-      <c r="A10" s="82"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="95"/>
+      <c r="A10" s="142"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="137"/>
       <c r="E10" s="23" t="str">
         <f>'Beneficiary Categories'!A15</f>
         <v>Medium Enterprises</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G10" s="9">
         <v>0</v>
@@ -3249,27 +6203,27 @@
         <v>4</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="161.25" customHeight="1">
-      <c r="A11" s="80">
+      <c r="A11" s="130">
         <v>134019</v>
       </c>
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="131" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="126" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="129">
+        <v>3000000</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="82" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="83">
-        <v>3000000</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="F11" s="14" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -3277,20 +6231,20 @@
       <c r="H11" s="4">
         <v>70</v>
       </c>
-      <c r="I11" s="84" t="s">
-        <v>54</v>
+      <c r="I11" s="133" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="91.5">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="83"/>
+      <c r="A12" s="130"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="129"/>
       <c r="E12" s="6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G12" s="16">
         <v>0</v>
@@ -3298,23 +6252,23 @@
       <c r="H12" s="16">
         <v>20</v>
       </c>
-      <c r="I12" s="84"/>
+      <c r="I12" s="133"/>
     </row>
     <row r="13" spans="1:10" ht="183" customHeight="1">
-      <c r="A13" s="88">
+      <c r="A13" s="141">
         <v>117633</v>
       </c>
-      <c r="B13" s="89" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="90" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="83">
+      <c r="B13" s="127" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="128" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="129">
         <v>2201100</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>41</v>
@@ -3323,43 +6277,43 @@
         <v>0</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="168" customHeight="1">
-      <c r="A14" s="82"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="83"/>
+      <c r="A14" s="142"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="129"/>
       <c r="E14" s="17" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G14" s="9">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30.75">
-      <c r="A15" s="82"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="83"/>
+      <c r="A15" s="142"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="128"/>
+      <c r="D15" s="129"/>
       <c r="E15" s="17" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="G15" s="9">
         <v>0</v>
@@ -3368,40 +6322,40 @@
         <v>3</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="76.5">
-      <c r="A16" s="82"/>
-      <c r="B16" s="89"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="83"/>
+      <c r="A16" s="142"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="129"/>
       <c r="E16" s="17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G16" s="9">
         <v>0</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="76.5">
-      <c r="A17" s="82"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="83"/>
+      <c r="A17" s="142"/>
+      <c r="B17" s="127"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="129"/>
       <c r="E17" s="17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G17" s="9">
         <v>0</v>
@@ -3410,16 +6364,16 @@
         <v>46</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="121.5">
-      <c r="A18" s="82"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="83"/>
+      <c r="A18" s="142"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="129"/>
       <c r="E18" s="17" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
@@ -3431,7 +6385,7 @@
         <v>6</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3463,7 +6417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8BE44E-B3DD-45CE-BB67-AA20DED67543}">
   <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3472,179 +6426,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="68" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="72" t="s">
-        <v>104</v>
+      <c r="A2" s="160" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="69" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="160" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="160" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="69" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="160" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="69" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="160" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="160" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="69" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="160" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="69" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="160" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="167" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="160" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" s="167" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="160" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="69" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="160" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="167" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="160" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="167" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="160" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="167" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="160" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="167" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30.75">
+      <c r="A17" s="160" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="96" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="72" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="96" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" s="72" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="96" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="72" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="96" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="72" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="96" t="s">
+      <c r="B17" s="69" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30.75">
+      <c r="A18" s="160" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="167" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="76.5">
+      <c r="A19" s="160" t="s">
+        <v>180</v>
+      </c>
+      <c r="B19" s="167" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30.75">
+      <c r="A20" s="160" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" s="167" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45.75">
+      <c r="A21" s="160" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="148" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30.75">
+      <c r="A22" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="72" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="96" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="96" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="97" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="96" t="s">
-        <v>119</v>
-      </c>
-      <c r="B11" s="97" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="96" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" s="72" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="96" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="97" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="96" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="97" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="96" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="97" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="96" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="97" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="96" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="96" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="97" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="96" t="s">
-        <v>130</v>
-      </c>
-      <c r="B19" s="97" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="96" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="97" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="96" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="98" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="96" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="97" t="s">
-        <v>135</v>
+      <c r="B22" s="167" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -3653,26 +6607,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3927,14 +6861,51 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Nguyen Vu Linh</DisplayName>
+        <AccountId>2515</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Trinh Thi Bich Thuy</DisplayName>
+        <AccountId>1771</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Nguyen Thi Thu Ha</DisplayName>
+        <AccountId>2510</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9EA5A6B-4907-41A1-A8C7-9BE3F53C78B4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2295D2-686C-4E88-AC90-9CDCBA3A093B}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{242C6A4E-D5F7-40A6-BE63-872510DEAD3D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9EA5A6B-4907-41A1-A8C7-9BE3F53C78B4}"/>
 </file>
--- a/01_Input/00_CO Validation/Viet Nam - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Viet Nam - Energy Projects.xlsx
@@ -963,11 +963,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1064,6 +1064,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K13" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3629,9 +3649,10 @@
       <c r="F10" s="59" t="n"/>
       <c r="G10" s="59" t="n"/>
       <c r="H10" s="59" t="n"/>
-      <c r="I10" s="23">
-        <f>'Beneficiary Categories'!A15</f>
-        <v/>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>Medium Enterprises</t>
+        </is>
       </c>
       <c r="J10" s="41" t="inlineStr">
         <is>
@@ -3806,15 +3827,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="181" t="n"/>
-      <c r="M13" s="182" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="K13" s="181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="182" t="n"/>
+      <c r="M13" s="133" t="n"/>
       <c r="N13" s="75" t="n"/>
       <c r="O13" s="127" t="n"/>
       <c r="P13" s="126" t="n"/>
@@ -4148,7 +4165,7 @@
       <c r="X19" s="76" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -4179,18 +4196,13 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -4715,9 +4727,10 @@
       <c r="B11" s="186" t="n"/>
       <c r="C11" s="186" t="n"/>
       <c r="D11" s="186" t="n"/>
-      <c r="E11" s="23">
-        <f>'Beneficiary Categories'!A15</f>
-        <v/>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>Medium Enterprises</t>
+        </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -5952,9 +5965,10 @@
       <c r="B10" s="186" t="n"/>
       <c r="C10" s="186" t="n"/>
       <c r="D10" s="186" t="n"/>
-      <c r="E10" s="23">
-        <f>'Beneficiary Categories'!A15</f>
-        <v/>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Medium Enterprises</t>
+        </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
@@ -6612,9 +6626,10 @@
       <c r="B4" s="186" t="n"/>
       <c r="C4" s="186" t="n"/>
       <c r="D4" s="186" t="n"/>
-      <c r="E4" s="3">
-        <f>E2</f>
-        <v/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Policy or Regulatory Framework and pilot activities </t>
+        </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -6785,9 +6800,10 @@
       <c r="B10" s="186" t="n"/>
       <c r="C10" s="186" t="n"/>
       <c r="D10" s="186" t="n"/>
-      <c r="E10" s="23">
-        <f>'Beneficiary Categories'!A15</f>
-        <v/>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Medium Enterprises</t>
+        </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
